--- a/CryoGrid/CryoGridCommunity_results/templates/automatic_loops/loop1/loop1.xlsx
+++ b/CryoGrid/CryoGridCommunity_results/templates/automatic_loops/loop1/loop1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="182" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="183" uniqueCount="97">
   <si>
     <t>-------------------</t>
   </si>
@@ -223,19 +223,22 @@
     <t>FORCING_data_01Aug1958_01Aug2024_MON1</t>
   </si>
   <si>
+    <t>..\..\forcing\Forcing_Data\</t>
+  </si>
+  <si>
+    <t>01.09.</t>
+  </si>
+  <si>
+    <t>regridded</t>
+  </si>
+  <si>
+    <t>all_lateral</t>
+  </si>
+  <si>
+    <t>snow_all</t>
+  </si>
+  <si>
     <t>D:\Utilisateurs\pozsgayv\Documents\CryoGrid_VP_Workflow\forcing\Forcing_Data\</t>
-  </si>
-  <si>
-    <t>01.09.</t>
-  </si>
-  <si>
-    <t>regridded</t>
-  </si>
-  <si>
-    <t>all_lateral</t>
-  </si>
-  <si>
-    <t>snow_all</t>
   </si>
   <si>
     <t>default value</t>
@@ -347,12 +350,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V121"/>
+  <dimension ref="A1:J121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.453125" customWidth="true"/>
     <col min="2" max="2" width="114.7265625" customWidth="true"/>
-    <col min="3" max="3" width="21.90625" customWidth="true"/>
+    <col min="3" max="3" width="71.08984375" customWidth="true"/>
     <col min="4" max="4" width="118.7265625" customWidth="true"/>
     <col min="5" max="5" width="12.90625" customWidth="true"/>
     <col min="6" max="6" width="8.08984375" customWidth="true"/>
@@ -360,18 +363,6 @@
     <col min="8" max="8" width="78.81640625" customWidth="true"/>
     <col min="9" max="9" width="9.140625"/>
     <col min="10" max="10" width="9.140625"/>
-    <col min="11" max="11" width="9.140625"/>
-    <col min="12" max="12" width="9.140625"/>
-    <col min="13" max="13" width="9.140625"/>
-    <col min="14" max="14" width="9.140625"/>
-    <col min="15" max="15" width="9.140625"/>
-    <col min="16" max="16" width="9.140625"/>
-    <col min="17" max="17" width="9.140625"/>
-    <col min="18" max="18" width="9.140625"/>
-    <col min="19" max="19" width="9.140625"/>
-    <col min="20" max="20" width="9.140625"/>
-    <col min="21" max="21" width="9.140625"/>
-    <col min="22" max="22" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -387,18 +378,6 @@
       <c r="H1" s="0"/>
       <c r="I1" s="0"/>
       <c r="J1" s="0"/>
-      <c r="K1" s="0"/>
-      <c r="L1" s="0"/>
-      <c r="M1" s="0"/>
-      <c r="N1" s="0"/>
-      <c r="O1" s="0"/>
-      <c r="P1" s="0"/>
-      <c r="Q1" s="0"/>
-      <c r="R1" s="0"/>
-      <c r="S1" s="0"/>
-      <c r="T1" s="0"/>
-      <c r="U1" s="0"/>
-      <c r="V1" s="0"/>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
@@ -415,18 +394,6 @@
       <c r="H2" s="0"/>
       <c r="I2" s="0"/>
       <c r="J2" s="0"/>
-      <c r="K2" s="0"/>
-      <c r="L2" s="0"/>
-      <c r="M2" s="0"/>
-      <c r="N2" s="0"/>
-      <c r="O2" s="0"/>
-      <c r="P2" s="0"/>
-      <c r="Q2" s="0"/>
-      <c r="R2" s="0"/>
-      <c r="S2" s="0"/>
-      <c r="T2" s="0"/>
-      <c r="U2" s="0"/>
-      <c r="V2" s="0"/>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
@@ -443,18 +410,6 @@
       <c r="H3" s="0"/>
       <c r="I3" s="0"/>
       <c r="J3" s="0"/>
-      <c r="K3" s="0"/>
-      <c r="L3" s="0"/>
-      <c r="M3" s="0"/>
-      <c r="N3" s="0"/>
-      <c r="O3" s="0"/>
-      <c r="P3" s="0"/>
-      <c r="Q3" s="0"/>
-      <c r="R3" s="0"/>
-      <c r="S3" s="0"/>
-      <c r="T3" s="0"/>
-      <c r="U3" s="0"/>
-      <c r="V3" s="0"/>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
@@ -471,18 +426,6 @@
       <c r="H4" s="0"/>
       <c r="I4" s="0"/>
       <c r="J4" s="0"/>
-      <c r="K4" s="0"/>
-      <c r="L4" s="0"/>
-      <c r="M4" s="0"/>
-      <c r="N4" s="0"/>
-      <c r="O4" s="0"/>
-      <c r="P4" s="0"/>
-      <c r="Q4" s="0"/>
-      <c r="R4" s="0"/>
-      <c r="S4" s="0"/>
-      <c r="T4" s="0"/>
-      <c r="U4" s="0"/>
-      <c r="V4" s="0"/>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
@@ -499,18 +442,6 @@
       <c r="H5" s="0"/>
       <c r="I5" s="0"/>
       <c r="J5" s="0"/>
-      <c r="K5" s="0"/>
-      <c r="L5" s="0"/>
-      <c r="M5" s="0"/>
-      <c r="N5" s="0"/>
-      <c r="O5" s="0"/>
-      <c r="P5" s="0"/>
-      <c r="Q5" s="0"/>
-      <c r="R5" s="0"/>
-      <c r="S5" s="0"/>
-      <c r="T5" s="0"/>
-      <c r="U5" s="0"/>
-      <c r="V5" s="0"/>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
@@ -526,25 +457,13 @@
         <v>20</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F6" s="0"/>
       <c r="G6" s="0"/>
       <c r="H6" s="0"/>
       <c r="I6" s="0"/>
       <c r="J6" s="0"/>
-      <c r="K6" s="0"/>
-      <c r="L6" s="0"/>
-      <c r="M6" s="0"/>
-      <c r="N6" s="0"/>
-      <c r="O6" s="0"/>
-      <c r="P6" s="0"/>
-      <c r="Q6" s="0"/>
-      <c r="R6" s="0"/>
-      <c r="S6" s="0"/>
-      <c r="T6" s="0"/>
-      <c r="U6" s="0"/>
-      <c r="V6" s="0"/>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
@@ -560,25 +479,13 @@
         <v>2</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F7" s="0"/>
       <c r="G7" s="0"/>
       <c r="H7" s="0"/>
       <c r="I7" s="0"/>
       <c r="J7" s="0"/>
-      <c r="K7" s="0"/>
-      <c r="L7" s="0"/>
-      <c r="M7" s="0"/>
-      <c r="N7" s="0"/>
-      <c r="O7" s="0"/>
-      <c r="P7" s="0"/>
-      <c r="Q7" s="0"/>
-      <c r="R7" s="0"/>
-      <c r="S7" s="0"/>
-      <c r="T7" s="0"/>
-      <c r="U7" s="0"/>
-      <c r="V7" s="0"/>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
@@ -594,25 +501,13 @@
         <v>1</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F8" s="0"/>
       <c r="G8" s="0"/>
       <c r="H8" s="0"/>
       <c r="I8" s="0"/>
       <c r="J8" s="0"/>
-      <c r="K8" s="0"/>
-      <c r="L8" s="0"/>
-      <c r="M8" s="0"/>
-      <c r="N8" s="0"/>
-      <c r="O8" s="0"/>
-      <c r="P8" s="0"/>
-      <c r="Q8" s="0"/>
-      <c r="R8" s="0"/>
-      <c r="S8" s="0"/>
-      <c r="T8" s="0"/>
-      <c r="U8" s="0"/>
-      <c r="V8" s="0"/>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
@@ -627,18 +522,6 @@
       <c r="H9" s="0"/>
       <c r="I9" s="0"/>
       <c r="J9" s="0"/>
-      <c r="K9" s="0"/>
-      <c r="L9" s="0"/>
-      <c r="M9" s="0"/>
-      <c r="N9" s="0"/>
-      <c r="O9" s="0"/>
-      <c r="P9" s="0"/>
-      <c r="Q9" s="0"/>
-      <c r="R9" s="0"/>
-      <c r="S9" s="0"/>
-      <c r="T9" s="0"/>
-      <c r="U9" s="0"/>
-      <c r="V9" s="0"/>
     </row>
     <row r="10">
       <c r="A10" s="0"/>
@@ -651,18 +534,6 @@
       <c r="H10" s="0"/>
       <c r="I10" s="0"/>
       <c r="J10" s="0"/>
-      <c r="K10" s="0"/>
-      <c r="L10" s="0"/>
-      <c r="M10" s="0"/>
-      <c r="N10" s="0"/>
-      <c r="O10" s="0"/>
-      <c r="P10" s="0"/>
-      <c r="Q10" s="0"/>
-      <c r="R10" s="0"/>
-      <c r="S10" s="0"/>
-      <c r="T10" s="0"/>
-      <c r="U10" s="0"/>
-      <c r="V10" s="0"/>
     </row>
     <row r="11">
       <c r="A11" s="0"/>
@@ -675,18 +546,6 @@
       <c r="H11" s="0"/>
       <c r="I11" s="0"/>
       <c r="J11" s="0"/>
-      <c r="K11" s="0"/>
-      <c r="L11" s="0"/>
-      <c r="M11" s="0"/>
-      <c r="N11" s="0"/>
-      <c r="O11" s="0"/>
-      <c r="P11" s="0"/>
-      <c r="Q11" s="0"/>
-      <c r="R11" s="0"/>
-      <c r="S11" s="0"/>
-      <c r="T11" s="0"/>
-      <c r="U11" s="0"/>
-      <c r="V11" s="0"/>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
@@ -701,18 +560,6 @@
       <c r="H12" s="0"/>
       <c r="I12" s="0"/>
       <c r="J12" s="0"/>
-      <c r="K12" s="0"/>
-      <c r="L12" s="0"/>
-      <c r="M12" s="0"/>
-      <c r="N12" s="0"/>
-      <c r="O12" s="0"/>
-      <c r="P12" s="0"/>
-      <c r="Q12" s="0"/>
-      <c r="R12" s="0"/>
-      <c r="S12" s="0"/>
-      <c r="T12" s="0"/>
-      <c r="U12" s="0"/>
-      <c r="V12" s="0"/>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
@@ -729,18 +576,6 @@
       <c r="H13" s="0"/>
       <c r="I13" s="0"/>
       <c r="J13" s="0"/>
-      <c r="K13" s="0"/>
-      <c r="L13" s="0"/>
-      <c r="M13" s="0"/>
-      <c r="N13" s="0"/>
-      <c r="O13" s="0"/>
-      <c r="P13" s="0"/>
-      <c r="Q13" s="0"/>
-      <c r="R13" s="0"/>
-      <c r="S13" s="0"/>
-      <c r="T13" s="0"/>
-      <c r="U13" s="0"/>
-      <c r="V13" s="0"/>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
@@ -757,18 +592,6 @@
       <c r="H14" s="0"/>
       <c r="I14" s="0"/>
       <c r="J14" s="0"/>
-      <c r="K14" s="0"/>
-      <c r="L14" s="0"/>
-      <c r="M14" s="0"/>
-      <c r="N14" s="0"/>
-      <c r="O14" s="0"/>
-      <c r="P14" s="0"/>
-      <c r="Q14" s="0"/>
-      <c r="R14" s="0"/>
-      <c r="S14" s="0"/>
-      <c r="T14" s="0"/>
-      <c r="U14" s="0"/>
-      <c r="V14" s="0"/>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
@@ -785,18 +608,6 @@
       <c r="H15" s="0"/>
       <c r="I15" s="0"/>
       <c r="J15" s="0"/>
-      <c r="K15" s="0"/>
-      <c r="L15" s="0"/>
-      <c r="M15" s="0"/>
-      <c r="N15" s="0"/>
-      <c r="O15" s="0"/>
-      <c r="P15" s="0"/>
-      <c r="Q15" s="0"/>
-      <c r="R15" s="0"/>
-      <c r="S15" s="0"/>
-      <c r="T15" s="0"/>
-      <c r="U15" s="0"/>
-      <c r="V15" s="0"/>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
@@ -813,18 +624,6 @@
       <c r="H16" s="0"/>
       <c r="I16" s="0"/>
       <c r="J16" s="0"/>
-      <c r="K16" s="0"/>
-      <c r="L16" s="0"/>
-      <c r="M16" s="0"/>
-      <c r="N16" s="0"/>
-      <c r="O16" s="0"/>
-      <c r="P16" s="0"/>
-      <c r="Q16" s="0"/>
-      <c r="R16" s="0"/>
-      <c r="S16" s="0"/>
-      <c r="T16" s="0"/>
-      <c r="U16" s="0"/>
-      <c r="V16" s="0"/>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
@@ -841,18 +640,6 @@
       <c r="H17" s="0"/>
       <c r="I17" s="0"/>
       <c r="J17" s="0"/>
-      <c r="K17" s="0"/>
-      <c r="L17" s="0"/>
-      <c r="M17" s="0"/>
-      <c r="N17" s="0"/>
-      <c r="O17" s="0"/>
-      <c r="P17" s="0"/>
-      <c r="Q17" s="0"/>
-      <c r="R17" s="0"/>
-      <c r="S17" s="0"/>
-      <c r="T17" s="0"/>
-      <c r="U17" s="0"/>
-      <c r="V17" s="0"/>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
@@ -869,18 +656,6 @@
       <c r="H18" s="0"/>
       <c r="I18" s="0"/>
       <c r="J18" s="0"/>
-      <c r="K18" s="0"/>
-      <c r="L18" s="0"/>
-      <c r="M18" s="0"/>
-      <c r="N18" s="0"/>
-      <c r="O18" s="0"/>
-      <c r="P18" s="0"/>
-      <c r="Q18" s="0"/>
-      <c r="R18" s="0"/>
-      <c r="S18" s="0"/>
-      <c r="T18" s="0"/>
-      <c r="U18" s="0"/>
-      <c r="V18" s="0"/>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
@@ -897,18 +672,6 @@
       <c r="H19" s="0"/>
       <c r="I19" s="0"/>
       <c r="J19" s="0"/>
-      <c r="K19" s="0"/>
-      <c r="L19" s="0"/>
-      <c r="M19" s="0"/>
-      <c r="N19" s="0"/>
-      <c r="O19" s="0"/>
-      <c r="P19" s="0"/>
-      <c r="Q19" s="0"/>
-      <c r="R19" s="0"/>
-      <c r="S19" s="0"/>
-      <c r="T19" s="0"/>
-      <c r="U19" s="0"/>
-      <c r="V19" s="0"/>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
@@ -925,18 +688,6 @@
       <c r="H20" s="0"/>
       <c r="I20" s="0"/>
       <c r="J20" s="0"/>
-      <c r="K20" s="0"/>
-      <c r="L20" s="0"/>
-      <c r="M20" s="0"/>
-      <c r="N20" s="0"/>
-      <c r="O20" s="0"/>
-      <c r="P20" s="0"/>
-      <c r="Q20" s="0"/>
-      <c r="R20" s="0"/>
-      <c r="S20" s="0"/>
-      <c r="T20" s="0"/>
-      <c r="U20" s="0"/>
-      <c r="V20" s="0"/>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
@@ -953,18 +704,6 @@
       <c r="H21" s="0"/>
       <c r="I21" s="0"/>
       <c r="J21" s="0"/>
-      <c r="K21" s="0"/>
-      <c r="L21" s="0"/>
-      <c r="M21" s="0"/>
-      <c r="N21" s="0"/>
-      <c r="O21" s="0"/>
-      <c r="P21" s="0"/>
-      <c r="Q21" s="0"/>
-      <c r="R21" s="0"/>
-      <c r="S21" s="0"/>
-      <c r="T21" s="0"/>
-      <c r="U21" s="0"/>
-      <c r="V21" s="0"/>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
@@ -979,18 +718,6 @@
       <c r="H22" s="0"/>
       <c r="I22" s="0"/>
       <c r="J22" s="0"/>
-      <c r="K22" s="0"/>
-      <c r="L22" s="0"/>
-      <c r="M22" s="0"/>
-      <c r="N22" s="0"/>
-      <c r="O22" s="0"/>
-      <c r="P22" s="0"/>
-      <c r="Q22" s="0"/>
-      <c r="R22" s="0"/>
-      <c r="S22" s="0"/>
-      <c r="T22" s="0"/>
-      <c r="U22" s="0"/>
-      <c r="V22" s="0"/>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
@@ -1005,18 +732,6 @@
       <c r="H23" s="0"/>
       <c r="I23" s="0"/>
       <c r="J23" s="0"/>
-      <c r="K23" s="0"/>
-      <c r="L23" s="0"/>
-      <c r="M23" s="0"/>
-      <c r="N23" s="0"/>
-      <c r="O23" s="0"/>
-      <c r="P23" s="0"/>
-      <c r="Q23" s="0"/>
-      <c r="R23" s="0"/>
-      <c r="S23" s="0"/>
-      <c r="T23" s="0"/>
-      <c r="U23" s="0"/>
-      <c r="V23" s="0"/>
     </row>
     <row r="24">
       <c r="A24" s="0"/>
@@ -1029,18 +744,6 @@
       <c r="H24" s="0"/>
       <c r="I24" s="0"/>
       <c r="J24" s="0"/>
-      <c r="K24" s="0"/>
-      <c r="L24" s="0"/>
-      <c r="M24" s="0"/>
-      <c r="N24" s="0"/>
-      <c r="O24" s="0"/>
-      <c r="P24" s="0"/>
-      <c r="Q24" s="0"/>
-      <c r="R24" s="0"/>
-      <c r="S24" s="0"/>
-      <c r="T24" s="0"/>
-      <c r="U24" s="0"/>
-      <c r="V24" s="0"/>
     </row>
     <row r="25">
       <c r="A25" s="0"/>
@@ -1053,18 +756,6 @@
       <c r="H25" s="0"/>
       <c r="I25" s="0"/>
       <c r="J25" s="0"/>
-      <c r="K25" s="0"/>
-      <c r="L25" s="0"/>
-      <c r="M25" s="0"/>
-      <c r="N25" s="0"/>
-      <c r="O25" s="0"/>
-      <c r="P25" s="0"/>
-      <c r="Q25" s="0"/>
-      <c r="R25" s="0"/>
-      <c r="S25" s="0"/>
-      <c r="T25" s="0"/>
-      <c r="U25" s="0"/>
-      <c r="V25" s="0"/>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
@@ -1079,18 +770,6 @@
       <c r="H26" s="0"/>
       <c r="I26" s="0"/>
       <c r="J26" s="0"/>
-      <c r="K26" s="0"/>
-      <c r="L26" s="0"/>
-      <c r="M26" s="0"/>
-      <c r="N26" s="0"/>
-      <c r="O26" s="0"/>
-      <c r="P26" s="0"/>
-      <c r="Q26" s="0"/>
-      <c r="R26" s="0"/>
-      <c r="S26" s="0"/>
-      <c r="T26" s="0"/>
-      <c r="U26" s="0"/>
-      <c r="V26" s="0"/>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
@@ -1107,18 +786,6 @@
       <c r="H27" s="0"/>
       <c r="I27" s="0"/>
       <c r="J27" s="0"/>
-      <c r="K27" s="0"/>
-      <c r="L27" s="0"/>
-      <c r="M27" s="0"/>
-      <c r="N27" s="0"/>
-      <c r="O27" s="0"/>
-      <c r="P27" s="0"/>
-      <c r="Q27" s="0"/>
-      <c r="R27" s="0"/>
-      <c r="S27" s="0"/>
-      <c r="T27" s="0"/>
-      <c r="U27" s="0"/>
-      <c r="V27" s="0"/>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
@@ -1135,18 +802,6 @@
       <c r="H28" s="0"/>
       <c r="I28" s="0"/>
       <c r="J28" s="0"/>
-      <c r="K28" s="0"/>
-      <c r="L28" s="0"/>
-      <c r="M28" s="0"/>
-      <c r="N28" s="0"/>
-      <c r="O28" s="0"/>
-      <c r="P28" s="0"/>
-      <c r="Q28" s="0"/>
-      <c r="R28" s="0"/>
-      <c r="S28" s="0"/>
-      <c r="T28" s="0"/>
-      <c r="U28" s="0"/>
-      <c r="V28" s="0"/>
     </row>
     <row r="29">
       <c r="A29" s="0"/>
@@ -1159,18 +814,6 @@
       <c r="H29" s="0"/>
       <c r="I29" s="0"/>
       <c r="J29" s="0"/>
-      <c r="K29" s="0"/>
-      <c r="L29" s="0"/>
-      <c r="M29" s="0"/>
-      <c r="N29" s="0"/>
-      <c r="O29" s="0"/>
-      <c r="P29" s="0"/>
-      <c r="Q29" s="0"/>
-      <c r="R29" s="0"/>
-      <c r="S29" s="0"/>
-      <c r="T29" s="0"/>
-      <c r="U29" s="0"/>
-      <c r="V29" s="0"/>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
@@ -1187,18 +830,6 @@
       <c r="H30" s="0"/>
       <c r="I30" s="0"/>
       <c r="J30" s="0"/>
-      <c r="K30" s="0"/>
-      <c r="L30" s="0"/>
-      <c r="M30" s="0"/>
-      <c r="N30" s="0"/>
-      <c r="O30" s="0"/>
-      <c r="P30" s="0"/>
-      <c r="Q30" s="0"/>
-      <c r="R30" s="0"/>
-      <c r="S30" s="0"/>
-      <c r="T30" s="0"/>
-      <c r="U30" s="0"/>
-      <c r="V30" s="0"/>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
@@ -1215,18 +846,6 @@
       <c r="H31" s="0"/>
       <c r="I31" s="0"/>
       <c r="J31" s="0"/>
-      <c r="K31" s="0"/>
-      <c r="L31" s="0"/>
-      <c r="M31" s="0"/>
-      <c r="N31" s="0"/>
-      <c r="O31" s="0"/>
-      <c r="P31" s="0"/>
-      <c r="Q31" s="0"/>
-      <c r="R31" s="0"/>
-      <c r="S31" s="0"/>
-      <c r="T31" s="0"/>
-      <c r="U31" s="0"/>
-      <c r="V31" s="0"/>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
@@ -1243,18 +862,6 @@
       <c r="H32" s="0"/>
       <c r="I32" s="0"/>
       <c r="J32" s="0"/>
-      <c r="K32" s="0"/>
-      <c r="L32" s="0"/>
-      <c r="M32" s="0"/>
-      <c r="N32" s="0"/>
-      <c r="O32" s="0"/>
-      <c r="P32" s="0"/>
-      <c r="Q32" s="0"/>
-      <c r="R32" s="0"/>
-      <c r="S32" s="0"/>
-      <c r="T32" s="0"/>
-      <c r="U32" s="0"/>
-      <c r="V32" s="0"/>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
@@ -1267,7 +874,7 @@
         <v>46</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E33" s="0"/>
       <c r="F33" s="0"/>
@@ -1275,18 +882,6 @@
       <c r="H33" s="0"/>
       <c r="I33" s="0"/>
       <c r="J33" s="0"/>
-      <c r="K33" s="0"/>
-      <c r="L33" s="0"/>
-      <c r="M33" s="0"/>
-      <c r="N33" s="0"/>
-      <c r="O33" s="0"/>
-      <c r="P33" s="0"/>
-      <c r="Q33" s="0"/>
-      <c r="R33" s="0"/>
-      <c r="S33" s="0"/>
-      <c r="T33" s="0"/>
-      <c r="U33" s="0"/>
-      <c r="V33" s="0"/>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
@@ -1299,7 +894,7 @@
         <v>1</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E34" s="0"/>
       <c r="F34" s="0"/>
@@ -1307,18 +902,6 @@
       <c r="H34" s="0"/>
       <c r="I34" s="0"/>
       <c r="J34" s="0"/>
-      <c r="K34" s="0"/>
-      <c r="L34" s="0"/>
-      <c r="M34" s="0"/>
-      <c r="N34" s="0"/>
-      <c r="O34" s="0"/>
-      <c r="P34" s="0"/>
-      <c r="Q34" s="0"/>
-      <c r="R34" s="0"/>
-      <c r="S34" s="0"/>
-      <c r="T34" s="0"/>
-      <c r="U34" s="0"/>
-      <c r="V34" s="0"/>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
@@ -1333,18 +916,6 @@
       <c r="H35" s="0"/>
       <c r="I35" s="0"/>
       <c r="J35" s="0"/>
-      <c r="K35" s="0"/>
-      <c r="L35" s="0"/>
-      <c r="M35" s="0"/>
-      <c r="N35" s="0"/>
-      <c r="O35" s="0"/>
-      <c r="P35" s="0"/>
-      <c r="Q35" s="0"/>
-      <c r="R35" s="0"/>
-      <c r="S35" s="0"/>
-      <c r="T35" s="0"/>
-      <c r="U35" s="0"/>
-      <c r="V35" s="0"/>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
@@ -1359,18 +930,6 @@
       <c r="H36" s="0"/>
       <c r="I36" s="0"/>
       <c r="J36" s="0"/>
-      <c r="K36" s="0"/>
-      <c r="L36" s="0"/>
-      <c r="M36" s="0"/>
-      <c r="N36" s="0"/>
-      <c r="O36" s="0"/>
-      <c r="P36" s="0"/>
-      <c r="Q36" s="0"/>
-      <c r="R36" s="0"/>
-      <c r="S36" s="0"/>
-      <c r="T36" s="0"/>
-      <c r="U36" s="0"/>
-      <c r="V36" s="0"/>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
@@ -1385,18 +944,6 @@
       <c r="H37" s="0"/>
       <c r="I37" s="0"/>
       <c r="J37" s="0"/>
-      <c r="K37" s="0"/>
-      <c r="L37" s="0"/>
-      <c r="M37" s="0"/>
-      <c r="N37" s="0"/>
-      <c r="O37" s="0"/>
-      <c r="P37" s="0"/>
-      <c r="Q37" s="0"/>
-      <c r="R37" s="0"/>
-      <c r="S37" s="0"/>
-      <c r="T37" s="0"/>
-      <c r="U37" s="0"/>
-      <c r="V37" s="0"/>
     </row>
     <row r="38">
       <c r="A38" s="0"/>
@@ -1409,18 +956,6 @@
       <c r="H38" s="0"/>
       <c r="I38" s="0"/>
       <c r="J38" s="0"/>
-      <c r="K38" s="0"/>
-      <c r="L38" s="0"/>
-      <c r="M38" s="0"/>
-      <c r="N38" s="0"/>
-      <c r="O38" s="0"/>
-      <c r="P38" s="0"/>
-      <c r="Q38" s="0"/>
-      <c r="R38" s="0"/>
-      <c r="S38" s="0"/>
-      <c r="T38" s="0"/>
-      <c r="U38" s="0"/>
-      <c r="V38" s="0"/>
     </row>
     <row r="39">
       <c r="A39" s="0"/>
@@ -1433,18 +968,6 @@
       <c r="H39" s="0"/>
       <c r="I39" s="0"/>
       <c r="J39" s="0"/>
-      <c r="K39" s="0"/>
-      <c r="L39" s="0"/>
-      <c r="M39" s="0"/>
-      <c r="N39" s="0"/>
-      <c r="O39" s="0"/>
-      <c r="P39" s="0"/>
-      <c r="Q39" s="0"/>
-      <c r="R39" s="0"/>
-      <c r="S39" s="0"/>
-      <c r="T39" s="0"/>
-      <c r="U39" s="0"/>
-      <c r="V39" s="0"/>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
@@ -1459,18 +982,6 @@
       <c r="H40" s="0"/>
       <c r="I40" s="0"/>
       <c r="J40" s="0"/>
-      <c r="K40" s="0"/>
-      <c r="L40" s="0"/>
-      <c r="M40" s="0"/>
-      <c r="N40" s="0"/>
-      <c r="O40" s="0"/>
-      <c r="P40" s="0"/>
-      <c r="Q40" s="0"/>
-      <c r="R40" s="0"/>
-      <c r="S40" s="0"/>
-      <c r="T40" s="0"/>
-      <c r="U40" s="0"/>
-      <c r="V40" s="0"/>
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
@@ -1487,18 +998,6 @@
       <c r="H41" s="0"/>
       <c r="I41" s="0"/>
       <c r="J41" s="0"/>
-      <c r="K41" s="0"/>
-      <c r="L41" s="0"/>
-      <c r="M41" s="0"/>
-      <c r="N41" s="0"/>
-      <c r="O41" s="0"/>
-      <c r="P41" s="0"/>
-      <c r="Q41" s="0"/>
-      <c r="R41" s="0"/>
-      <c r="S41" s="0"/>
-      <c r="T41" s="0"/>
-      <c r="U41" s="0"/>
-      <c r="V41" s="0"/>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
@@ -1515,18 +1014,6 @@
       <c r="H42" s="0"/>
       <c r="I42" s="0"/>
       <c r="J42" s="0"/>
-      <c r="K42" s="0"/>
-      <c r="L42" s="0"/>
-      <c r="M42" s="0"/>
-      <c r="N42" s="0"/>
-      <c r="O42" s="0"/>
-      <c r="P42" s="0"/>
-      <c r="Q42" s="0"/>
-      <c r="R42" s="0"/>
-      <c r="S42" s="0"/>
-      <c r="T42" s="0"/>
-      <c r="U42" s="0"/>
-      <c r="V42" s="0"/>
     </row>
     <row r="43">
       <c r="A43" s="0"/>
@@ -1539,18 +1026,6 @@
       <c r="H43" s="0"/>
       <c r="I43" s="0"/>
       <c r="J43" s="0"/>
-      <c r="K43" s="0"/>
-      <c r="L43" s="0"/>
-      <c r="M43" s="0"/>
-      <c r="N43" s="0"/>
-      <c r="O43" s="0"/>
-      <c r="P43" s="0"/>
-      <c r="Q43" s="0"/>
-      <c r="R43" s="0"/>
-      <c r="S43" s="0"/>
-      <c r="T43" s="0"/>
-      <c r="U43" s="0"/>
-      <c r="V43" s="0"/>
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
@@ -1567,18 +1042,6 @@
       <c r="H44" s="0"/>
       <c r="I44" s="0"/>
       <c r="J44" s="0"/>
-      <c r="K44" s="0"/>
-      <c r="L44" s="0"/>
-      <c r="M44" s="0"/>
-      <c r="N44" s="0"/>
-      <c r="O44" s="0"/>
-      <c r="P44" s="0"/>
-      <c r="Q44" s="0"/>
-      <c r="R44" s="0"/>
-      <c r="S44" s="0"/>
-      <c r="T44" s="0"/>
-      <c r="U44" s="0"/>
-      <c r="V44" s="0"/>
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
@@ -1595,18 +1058,6 @@
       <c r="H45" s="0"/>
       <c r="I45" s="0"/>
       <c r="J45" s="0"/>
-      <c r="K45" s="0"/>
-      <c r="L45" s="0"/>
-      <c r="M45" s="0"/>
-      <c r="N45" s="0"/>
-      <c r="O45" s="0"/>
-      <c r="P45" s="0"/>
-      <c r="Q45" s="0"/>
-      <c r="R45" s="0"/>
-      <c r="S45" s="0"/>
-      <c r="T45" s="0"/>
-      <c r="U45" s="0"/>
-      <c r="V45" s="0"/>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
@@ -1623,18 +1074,6 @@
       <c r="H46" s="0"/>
       <c r="I46" s="0"/>
       <c r="J46" s="0"/>
-      <c r="K46" s="0"/>
-      <c r="L46" s="0"/>
-      <c r="M46" s="0"/>
-      <c r="N46" s="0"/>
-      <c r="O46" s="0"/>
-      <c r="P46" s="0"/>
-      <c r="Q46" s="0"/>
-      <c r="R46" s="0"/>
-      <c r="S46" s="0"/>
-      <c r="T46" s="0"/>
-      <c r="U46" s="0"/>
-      <c r="V46" s="0"/>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
@@ -1653,24 +1092,12 @@
         <v>59</v>
       </c>
       <c r="F47" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G47" s="0"/>
       <c r="H47" s="0"/>
       <c r="I47" s="0"/>
       <c r="J47" s="0"/>
-      <c r="K47" s="0"/>
-      <c r="L47" s="0"/>
-      <c r="M47" s="0"/>
-      <c r="N47" s="0"/>
-      <c r="O47" s="0"/>
-      <c r="P47" s="0"/>
-      <c r="Q47" s="0"/>
-      <c r="R47" s="0"/>
-      <c r="S47" s="0"/>
-      <c r="T47" s="0"/>
-      <c r="U47" s="0"/>
-      <c r="V47" s="0"/>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
@@ -1689,24 +1116,12 @@
         <v>1</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G48" s="0"/>
       <c r="H48" s="0"/>
       <c r="I48" s="0"/>
       <c r="J48" s="0"/>
-      <c r="K48" s="0"/>
-      <c r="L48" s="0"/>
-      <c r="M48" s="0"/>
-      <c r="N48" s="0"/>
-      <c r="O48" s="0"/>
-      <c r="P48" s="0"/>
-      <c r="Q48" s="0"/>
-      <c r="R48" s="0"/>
-      <c r="S48" s="0"/>
-      <c r="T48" s="0"/>
-      <c r="U48" s="0"/>
-      <c r="V48" s="0"/>
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
@@ -1721,18 +1136,6 @@
       <c r="H49" s="0"/>
       <c r="I49" s="0"/>
       <c r="J49" s="0"/>
-      <c r="K49" s="0"/>
-      <c r="L49" s="0"/>
-      <c r="M49" s="0"/>
-      <c r="N49" s="0"/>
-      <c r="O49" s="0"/>
-      <c r="P49" s="0"/>
-      <c r="Q49" s="0"/>
-      <c r="R49" s="0"/>
-      <c r="S49" s="0"/>
-      <c r="T49" s="0"/>
-      <c r="U49" s="0"/>
-      <c r="V49" s="0"/>
     </row>
     <row r="50">
       <c r="A50" s="0"/>
@@ -1745,18 +1148,6 @@
       <c r="H50" s="0"/>
       <c r="I50" s="0"/>
       <c r="J50" s="0"/>
-      <c r="K50" s="0"/>
-      <c r="L50" s="0"/>
-      <c r="M50" s="0"/>
-      <c r="N50" s="0"/>
-      <c r="O50" s="0"/>
-      <c r="P50" s="0"/>
-      <c r="Q50" s="0"/>
-      <c r="R50" s="0"/>
-      <c r="S50" s="0"/>
-      <c r="T50" s="0"/>
-      <c r="U50" s="0"/>
-      <c r="V50" s="0"/>
     </row>
     <row r="51">
       <c r="A51" s="0"/>
@@ -1769,18 +1160,6 @@
       <c r="H51" s="0"/>
       <c r="I51" s="0"/>
       <c r="J51" s="0"/>
-      <c r="K51" s="0"/>
-      <c r="L51" s="0"/>
-      <c r="M51" s="0"/>
-      <c r="N51" s="0"/>
-      <c r="O51" s="0"/>
-      <c r="P51" s="0"/>
-      <c r="Q51" s="0"/>
-      <c r="R51" s="0"/>
-      <c r="S51" s="0"/>
-      <c r="T51" s="0"/>
-      <c r="U51" s="0"/>
-      <c r="V51" s="0"/>
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
@@ -1795,18 +1174,6 @@
       <c r="H52" s="0"/>
       <c r="I52" s="0"/>
       <c r="J52" s="0"/>
-      <c r="K52" s="0"/>
-      <c r="L52" s="0"/>
-      <c r="M52" s="0"/>
-      <c r="N52" s="0"/>
-      <c r="O52" s="0"/>
-      <c r="P52" s="0"/>
-      <c r="Q52" s="0"/>
-      <c r="R52" s="0"/>
-      <c r="S52" s="0"/>
-      <c r="T52" s="0"/>
-      <c r="U52" s="0"/>
-      <c r="V52" s="0"/>
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
@@ -1823,18 +1190,6 @@
       <c r="H53" s="0"/>
       <c r="I53" s="0"/>
       <c r="J53" s="0"/>
-      <c r="K53" s="0"/>
-      <c r="L53" s="0"/>
-      <c r="M53" s="0"/>
-      <c r="N53" s="0"/>
-      <c r="O53" s="0"/>
-      <c r="P53" s="0"/>
-      <c r="Q53" s="0"/>
-      <c r="R53" s="0"/>
-      <c r="S53" s="0"/>
-      <c r="T53" s="0"/>
-      <c r="U53" s="0"/>
-      <c r="V53" s="0"/>
     </row>
     <row r="54">
       <c r="A54" s="0" t="s">
@@ -1851,18 +1206,6 @@
       <c r="H54" s="0"/>
       <c r="I54" s="0"/>
       <c r="J54" s="0"/>
-      <c r="K54" s="0"/>
-      <c r="L54" s="0"/>
-      <c r="M54" s="0"/>
-      <c r="N54" s="0"/>
-      <c r="O54" s="0"/>
-      <c r="P54" s="0"/>
-      <c r="Q54" s="0"/>
-      <c r="R54" s="0"/>
-      <c r="S54" s="0"/>
-      <c r="T54" s="0"/>
-      <c r="U54" s="0"/>
-      <c r="V54" s="0"/>
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
@@ -1879,18 +1222,6 @@
       <c r="H55" s="0"/>
       <c r="I55" s="0"/>
       <c r="J55" s="0"/>
-      <c r="K55" s="0"/>
-      <c r="L55" s="0"/>
-      <c r="M55" s="0"/>
-      <c r="N55" s="0"/>
-      <c r="O55" s="0"/>
-      <c r="P55" s="0"/>
-      <c r="Q55" s="0"/>
-      <c r="R55" s="0"/>
-      <c r="S55" s="0"/>
-      <c r="T55" s="0"/>
-      <c r="U55" s="0"/>
-      <c r="V55" s="0"/>
     </row>
     <row r="56">
       <c r="A56" s="0" t="s">
@@ -1899,7 +1230,9 @@
       <c r="B56" s="0" t="s">
         <v>69</v>
       </c>
-      <c r="C56" s="0"/>
+      <c r="C56" s="0" t="s">
+        <v>74</v>
+      </c>
       <c r="D56" s="0"/>
       <c r="E56" s="0"/>
       <c r="F56" s="0"/>
@@ -1907,18 +1240,6 @@
       <c r="H56" s="0"/>
       <c r="I56" s="0"/>
       <c r="J56" s="0"/>
-      <c r="K56" s="0"/>
-      <c r="L56" s="0"/>
-      <c r="M56" s="0"/>
-      <c r="N56" s="0"/>
-      <c r="O56" s="0"/>
-      <c r="P56" s="0"/>
-      <c r="Q56" s="0"/>
-      <c r="R56" s="0"/>
-      <c r="S56" s="0"/>
-      <c r="T56" s="0"/>
-      <c r="U56" s="0"/>
-      <c r="V56" s="0"/>
     </row>
     <row r="57">
       <c r="A57" s="0" t="s">
@@ -1937,24 +1258,12 @@
         <v>1</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G57" s="0"/>
       <c r="H57" s="0"/>
       <c r="I57" s="0"/>
       <c r="J57" s="0"/>
-      <c r="K57" s="0"/>
-      <c r="L57" s="0"/>
-      <c r="M57" s="0"/>
-      <c r="N57" s="0"/>
-      <c r="O57" s="0"/>
-      <c r="P57" s="0"/>
-      <c r="Q57" s="0"/>
-      <c r="R57" s="0"/>
-      <c r="S57" s="0"/>
-      <c r="T57" s="0"/>
-      <c r="U57" s="0"/>
-      <c r="V57" s="0"/>
     </row>
     <row r="58">
       <c r="A58" s="0" t="s">
@@ -1973,24 +1282,12 @@
         <v>2</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G58" s="0"/>
       <c r="H58" s="0"/>
       <c r="I58" s="0"/>
       <c r="J58" s="0"/>
-      <c r="K58" s="0"/>
-      <c r="L58" s="0"/>
-      <c r="M58" s="0"/>
-      <c r="N58" s="0"/>
-      <c r="O58" s="0"/>
-      <c r="P58" s="0"/>
-      <c r="Q58" s="0"/>
-      <c r="R58" s="0"/>
-      <c r="S58" s="0"/>
-      <c r="T58" s="0"/>
-      <c r="U58" s="0"/>
-      <c r="V58" s="0"/>
     </row>
     <row r="59">
       <c r="A59" s="0" t="s">
@@ -2007,18 +1304,6 @@
       <c r="H59" s="0"/>
       <c r="I59" s="0"/>
       <c r="J59" s="0"/>
-      <c r="K59" s="0"/>
-      <c r="L59" s="0"/>
-      <c r="M59" s="0"/>
-      <c r="N59" s="0"/>
-      <c r="O59" s="0"/>
-      <c r="P59" s="0"/>
-      <c r="Q59" s="0"/>
-      <c r="R59" s="0"/>
-      <c r="S59" s="0"/>
-      <c r="T59" s="0"/>
-      <c r="U59" s="0"/>
-      <c r="V59" s="0"/>
     </row>
     <row r="60">
       <c r="A60" s="0" t="s">
@@ -2035,18 +1320,6 @@
       <c r="H60" s="0"/>
       <c r="I60" s="0"/>
       <c r="J60" s="0"/>
-      <c r="K60" s="0"/>
-      <c r="L60" s="0"/>
-      <c r="M60" s="0"/>
-      <c r="N60" s="0"/>
-      <c r="O60" s="0"/>
-      <c r="P60" s="0"/>
-      <c r="Q60" s="0"/>
-      <c r="R60" s="0"/>
-      <c r="S60" s="0"/>
-      <c r="T60" s="0"/>
-      <c r="U60" s="0"/>
-      <c r="V60" s="0"/>
     </row>
     <row r="61">
       <c r="A61" s="0" t="s">
@@ -2063,18 +1336,6 @@
       <c r="H61" s="0"/>
       <c r="I61" s="0"/>
       <c r="J61" s="0"/>
-      <c r="K61" s="0"/>
-      <c r="L61" s="0"/>
-      <c r="M61" s="0"/>
-      <c r="N61" s="0"/>
-      <c r="O61" s="0"/>
-      <c r="P61" s="0"/>
-      <c r="Q61" s="0"/>
-      <c r="R61" s="0"/>
-      <c r="S61" s="0"/>
-      <c r="T61" s="0"/>
-      <c r="U61" s="0"/>
-      <c r="V61" s="0"/>
     </row>
     <row r="62">
       <c r="A62" s="0" t="s">
@@ -2091,18 +1352,6 @@
       <c r="H62" s="0"/>
       <c r="I62" s="0"/>
       <c r="J62" s="0"/>
-      <c r="K62" s="0"/>
-      <c r="L62" s="0"/>
-      <c r="M62" s="0"/>
-      <c r="N62" s="0"/>
-      <c r="O62" s="0"/>
-      <c r="P62" s="0"/>
-      <c r="Q62" s="0"/>
-      <c r="R62" s="0"/>
-      <c r="S62" s="0"/>
-      <c r="T62" s="0"/>
-      <c r="U62" s="0"/>
-      <c r="V62" s="0"/>
     </row>
     <row r="63">
       <c r="A63" s="0" t="s">
@@ -2115,7 +1364,7 @@
         <v>43</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E63" s="0"/>
       <c r="F63" s="0"/>
@@ -2123,18 +1372,6 @@
       <c r="H63" s="0"/>
       <c r="I63" s="0"/>
       <c r="J63" s="0"/>
-      <c r="K63" s="0"/>
-      <c r="L63" s="0"/>
-      <c r="M63" s="0"/>
-      <c r="N63" s="0"/>
-      <c r="O63" s="0"/>
-      <c r="P63" s="0"/>
-      <c r="Q63" s="0"/>
-      <c r="R63" s="0"/>
-      <c r="S63" s="0"/>
-      <c r="T63" s="0"/>
-      <c r="U63" s="0"/>
-      <c r="V63" s="0"/>
     </row>
     <row r="64">
       <c r="A64" s="0" t="s">
@@ -2147,7 +1384,7 @@
         <v>1</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E64" s="0"/>
       <c r="F64" s="0"/>
@@ -2155,18 +1392,6 @@
       <c r="H64" s="0"/>
       <c r="I64" s="0"/>
       <c r="J64" s="0"/>
-      <c r="K64" s="0"/>
-      <c r="L64" s="0"/>
-      <c r="M64" s="0"/>
-      <c r="N64" s="0"/>
-      <c r="O64" s="0"/>
-      <c r="P64" s="0"/>
-      <c r="Q64" s="0"/>
-      <c r="R64" s="0"/>
-      <c r="S64" s="0"/>
-      <c r="T64" s="0"/>
-      <c r="U64" s="0"/>
-      <c r="V64" s="0"/>
     </row>
     <row r="65">
       <c r="A65" s="0" t="s">
@@ -2181,18 +1406,6 @@
       <c r="H65" s="0"/>
       <c r="I65" s="0"/>
       <c r="J65" s="0"/>
-      <c r="K65" s="0"/>
-      <c r="L65" s="0"/>
-      <c r="M65" s="0"/>
-      <c r="N65" s="0"/>
-      <c r="O65" s="0"/>
-      <c r="P65" s="0"/>
-      <c r="Q65" s="0"/>
-      <c r="R65" s="0"/>
-      <c r="S65" s="0"/>
-      <c r="T65" s="0"/>
-      <c r="U65" s="0"/>
-      <c r="V65" s="0"/>
     </row>
     <row r="66">
       <c r="A66" s="0"/>
@@ -2205,18 +1418,6 @@
       <c r="H66" s="0"/>
       <c r="I66" s="0"/>
       <c r="J66" s="0"/>
-      <c r="K66" s="0"/>
-      <c r="L66" s="0"/>
-      <c r="M66" s="0"/>
-      <c r="N66" s="0"/>
-      <c r="O66" s="0"/>
-      <c r="P66" s="0"/>
-      <c r="Q66" s="0"/>
-      <c r="R66" s="0"/>
-      <c r="S66" s="0"/>
-      <c r="T66" s="0"/>
-      <c r="U66" s="0"/>
-      <c r="V66" s="0"/>
     </row>
     <row r="67">
       <c r="A67" s="0" t="s">
@@ -2233,18 +1434,6 @@
       <c r="H67" s="0"/>
       <c r="I67" s="0"/>
       <c r="J67" s="0"/>
-      <c r="K67" s="0"/>
-      <c r="L67" s="0"/>
-      <c r="M67" s="0"/>
-      <c r="N67" s="0"/>
-      <c r="O67" s="0"/>
-      <c r="P67" s="0"/>
-      <c r="Q67" s="0"/>
-      <c r="R67" s="0"/>
-      <c r="S67" s="0"/>
-      <c r="T67" s="0"/>
-      <c r="U67" s="0"/>
-      <c r="V67" s="0"/>
     </row>
     <row r="68">
       <c r="A68" s="0" t="s">
@@ -2261,18 +1450,6 @@
       <c r="H68" s="0"/>
       <c r="I68" s="0"/>
       <c r="J68" s="0"/>
-      <c r="K68" s="0"/>
-      <c r="L68" s="0"/>
-      <c r="M68" s="0"/>
-      <c r="N68" s="0"/>
-      <c r="O68" s="0"/>
-      <c r="P68" s="0"/>
-      <c r="Q68" s="0"/>
-      <c r="R68" s="0"/>
-      <c r="S68" s="0"/>
-      <c r="T68" s="0"/>
-      <c r="U68" s="0"/>
-      <c r="V68" s="0"/>
     </row>
     <row r="69">
       <c r="A69" s="0" t="s">
@@ -2289,18 +1466,6 @@
       <c r="H69" s="0"/>
       <c r="I69" s="0"/>
       <c r="J69" s="0"/>
-      <c r="K69" s="0"/>
-      <c r="L69" s="0"/>
-      <c r="M69" s="0"/>
-      <c r="N69" s="0"/>
-      <c r="O69" s="0"/>
-      <c r="P69" s="0"/>
-      <c r="Q69" s="0"/>
-      <c r="R69" s="0"/>
-      <c r="S69" s="0"/>
-      <c r="T69" s="0"/>
-      <c r="U69" s="0"/>
-      <c r="V69" s="0"/>
     </row>
     <row r="70">
       <c r="A70" s="0" t="s">
@@ -2315,18 +1480,6 @@
       <c r="H70" s="0"/>
       <c r="I70" s="0"/>
       <c r="J70" s="0"/>
-      <c r="K70" s="0"/>
-      <c r="L70" s="0"/>
-      <c r="M70" s="0"/>
-      <c r="N70" s="0"/>
-      <c r="O70" s="0"/>
-      <c r="P70" s="0"/>
-      <c r="Q70" s="0"/>
-      <c r="R70" s="0"/>
-      <c r="S70" s="0"/>
-      <c r="T70" s="0"/>
-      <c r="U70" s="0"/>
-      <c r="V70" s="0"/>
     </row>
     <row r="71">
       <c r="A71" s="0"/>
@@ -2339,18 +1492,6 @@
       <c r="H71" s="0"/>
       <c r="I71" s="0"/>
       <c r="J71" s="0"/>
-      <c r="K71" s="0"/>
-      <c r="L71" s="0"/>
-      <c r="M71" s="0"/>
-      <c r="N71" s="0"/>
-      <c r="O71" s="0"/>
-      <c r="P71" s="0"/>
-      <c r="Q71" s="0"/>
-      <c r="R71" s="0"/>
-      <c r="S71" s="0"/>
-      <c r="T71" s="0"/>
-      <c r="U71" s="0"/>
-      <c r="V71" s="0"/>
     </row>
     <row r="72">
       <c r="A72" s="0"/>
@@ -2363,18 +1504,6 @@
       <c r="H72" s="0"/>
       <c r="I72" s="0"/>
       <c r="J72" s="0"/>
-      <c r="K72" s="0"/>
-      <c r="L72" s="0"/>
-      <c r="M72" s="0"/>
-      <c r="N72" s="0"/>
-      <c r="O72" s="0"/>
-      <c r="P72" s="0"/>
-      <c r="Q72" s="0"/>
-      <c r="R72" s="0"/>
-      <c r="S72" s="0"/>
-      <c r="T72" s="0"/>
-      <c r="U72" s="0"/>
-      <c r="V72" s="0"/>
     </row>
     <row r="73">
       <c r="A73" s="0" t="s">
@@ -2389,18 +1518,6 @@
       <c r="H73" s="0"/>
       <c r="I73" s="0"/>
       <c r="J73" s="0"/>
-      <c r="K73" s="0"/>
-      <c r="L73" s="0"/>
-      <c r="M73" s="0"/>
-      <c r="N73" s="0"/>
-      <c r="O73" s="0"/>
-      <c r="P73" s="0"/>
-      <c r="Q73" s="0"/>
-      <c r="R73" s="0"/>
-      <c r="S73" s="0"/>
-      <c r="T73" s="0"/>
-      <c r="U73" s="0"/>
-      <c r="V73" s="0"/>
     </row>
     <row r="74">
       <c r="A74" s="0" t="s">
@@ -2417,18 +1534,6 @@
       <c r="H74" s="0"/>
       <c r="I74" s="0"/>
       <c r="J74" s="0"/>
-      <c r="K74" s="0"/>
-      <c r="L74" s="0"/>
-      <c r="M74" s="0"/>
-      <c r="N74" s="0"/>
-      <c r="O74" s="0"/>
-      <c r="P74" s="0"/>
-      <c r="Q74" s="0"/>
-      <c r="R74" s="0"/>
-      <c r="S74" s="0"/>
-      <c r="T74" s="0"/>
-      <c r="U74" s="0"/>
-      <c r="V74" s="0"/>
     </row>
     <row r="75">
       <c r="A75" s="0" t="s">
@@ -2445,24 +1550,12 @@
       <c r="H75" s="0"/>
       <c r="I75" s="0"/>
       <c r="J75" s="0"/>
-      <c r="K75" s="0"/>
-      <c r="L75" s="0"/>
-      <c r="M75" s="0"/>
-      <c r="N75" s="0"/>
-      <c r="O75" s="0"/>
-      <c r="P75" s="0"/>
-      <c r="Q75" s="0"/>
-      <c r="R75" s="0"/>
-      <c r="S75" s="0"/>
-      <c r="T75" s="0"/>
-      <c r="U75" s="0"/>
-      <c r="V75" s="0"/>
     </row>
     <row r="76">
       <c r="A76" s="0"/>
       <c r="B76" s="0"/>
       <c r="C76" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D76" s="0"/>
       <c r="E76" s="0"/>
@@ -2471,18 +1564,6 @@
       <c r="H76" s="0"/>
       <c r="I76" s="0"/>
       <c r="J76" s="0"/>
-      <c r="K76" s="0"/>
-      <c r="L76" s="0"/>
-      <c r="M76" s="0"/>
-      <c r="N76" s="0"/>
-      <c r="O76" s="0"/>
-      <c r="P76" s="0"/>
-      <c r="Q76" s="0"/>
-      <c r="R76" s="0"/>
-      <c r="S76" s="0"/>
-      <c r="T76" s="0"/>
-      <c r="U76" s="0"/>
-      <c r="V76" s="0"/>
     </row>
     <row r="77">
       <c r="A77" s="0" t="s">
@@ -2495,7 +1576,7 @@
         <v>5</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E77" s="0"/>
       <c r="F77" s="0"/>
@@ -2503,18 +1584,6 @@
       <c r="H77" s="0"/>
       <c r="I77" s="0"/>
       <c r="J77" s="0"/>
-      <c r="K77" s="0"/>
-      <c r="L77" s="0"/>
-      <c r="M77" s="0"/>
-      <c r="N77" s="0"/>
-      <c r="O77" s="0"/>
-      <c r="P77" s="0"/>
-      <c r="Q77" s="0"/>
-      <c r="R77" s="0"/>
-      <c r="S77" s="0"/>
-      <c r="T77" s="0"/>
-      <c r="U77" s="0"/>
-      <c r="V77" s="0"/>
     </row>
     <row r="78">
       <c r="A78" s="0" t="s">
@@ -2529,18 +1598,6 @@
       <c r="H78" s="0"/>
       <c r="I78" s="0"/>
       <c r="J78" s="0"/>
-      <c r="K78" s="0"/>
-      <c r="L78" s="0"/>
-      <c r="M78" s="0"/>
-      <c r="N78" s="0"/>
-      <c r="O78" s="0"/>
-      <c r="P78" s="0"/>
-      <c r="Q78" s="0"/>
-      <c r="R78" s="0"/>
-      <c r="S78" s="0"/>
-      <c r="T78" s="0"/>
-      <c r="U78" s="0"/>
-      <c r="V78" s="0"/>
     </row>
     <row r="79">
       <c r="A79" s="0"/>
@@ -2553,18 +1610,6 @@
       <c r="H79" s="0"/>
       <c r="I79" s="0"/>
       <c r="J79" s="0"/>
-      <c r="K79" s="0"/>
-      <c r="L79" s="0"/>
-      <c r="M79" s="0"/>
-      <c r="N79" s="0"/>
-      <c r="O79" s="0"/>
-      <c r="P79" s="0"/>
-      <c r="Q79" s="0"/>
-      <c r="R79" s="0"/>
-      <c r="S79" s="0"/>
-      <c r="T79" s="0"/>
-      <c r="U79" s="0"/>
-      <c r="V79" s="0"/>
     </row>
     <row r="80">
       <c r="A80" s="0"/>
@@ -2577,18 +1622,6 @@
       <c r="H80" s="0"/>
       <c r="I80" s="0"/>
       <c r="J80" s="0"/>
-      <c r="K80" s="0"/>
-      <c r="L80" s="0"/>
-      <c r="M80" s="0"/>
-      <c r="N80" s="0"/>
-      <c r="O80" s="0"/>
-      <c r="P80" s="0"/>
-      <c r="Q80" s="0"/>
-      <c r="R80" s="0"/>
-      <c r="S80" s="0"/>
-      <c r="T80" s="0"/>
-      <c r="U80" s="0"/>
-      <c r="V80" s="0"/>
     </row>
     <row r="81">
       <c r="A81" s="0" t="s">
@@ -2603,18 +1636,6 @@
       <c r="H81" s="0"/>
       <c r="I81" s="0"/>
       <c r="J81" s="0"/>
-      <c r="K81" s="0"/>
-      <c r="L81" s="0"/>
-      <c r="M81" s="0"/>
-      <c r="N81" s="0"/>
-      <c r="O81" s="0"/>
-      <c r="P81" s="0"/>
-      <c r="Q81" s="0"/>
-      <c r="R81" s="0"/>
-      <c r="S81" s="0"/>
-      <c r="T81" s="0"/>
-      <c r="U81" s="0"/>
-      <c r="V81" s="0"/>
     </row>
     <row r="82">
       <c r="A82" s="0" t="s">
@@ -2631,18 +1652,6 @@
       <c r="H82" s="0"/>
       <c r="I82" s="0"/>
       <c r="J82" s="0"/>
-      <c r="K82" s="0"/>
-      <c r="L82" s="0"/>
-      <c r="M82" s="0"/>
-      <c r="N82" s="0"/>
-      <c r="O82" s="0"/>
-      <c r="P82" s="0"/>
-      <c r="Q82" s="0"/>
-      <c r="R82" s="0"/>
-      <c r="S82" s="0"/>
-      <c r="T82" s="0"/>
-      <c r="U82" s="0"/>
-      <c r="V82" s="0"/>
     </row>
     <row r="83">
       <c r="A83" s="0" t="s">
@@ -2653,7 +1662,7 @@
       </c>
       <c r="C83" s="0"/>
       <c r="D83" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E83" s="0"/>
       <c r="F83" s="0"/>
@@ -2661,24 +1670,12 @@
       <c r="H83" s="0"/>
       <c r="I83" s="0"/>
       <c r="J83" s="0"/>
-      <c r="K83" s="0"/>
-      <c r="L83" s="0"/>
-      <c r="M83" s="0"/>
-      <c r="N83" s="0"/>
-      <c r="O83" s="0"/>
-      <c r="P83" s="0"/>
-      <c r="Q83" s="0"/>
-      <c r="R83" s="0"/>
-      <c r="S83" s="0"/>
-      <c r="T83" s="0"/>
-      <c r="U83" s="0"/>
-      <c r="V83" s="0"/>
     </row>
     <row r="84">
       <c r="A84" s="0"/>
       <c r="B84" s="0"/>
       <c r="C84" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D84" s="0"/>
       <c r="E84" s="0"/>
@@ -2687,18 +1684,6 @@
       <c r="H84" s="0"/>
       <c r="I84" s="0"/>
       <c r="J84" s="0"/>
-      <c r="K84" s="0"/>
-      <c r="L84" s="0"/>
-      <c r="M84" s="0"/>
-      <c r="N84" s="0"/>
-      <c r="O84" s="0"/>
-      <c r="P84" s="0"/>
-      <c r="Q84" s="0"/>
-      <c r="R84" s="0"/>
-      <c r="S84" s="0"/>
-      <c r="T84" s="0"/>
-      <c r="U84" s="0"/>
-      <c r="V84" s="0"/>
     </row>
     <row r="85">
       <c r="A85" s="0" t="s">
@@ -2708,37 +1693,25 @@
         <v>63</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G85" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H85" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I85" s="0"/>
       <c r="J85" s="0"/>
-      <c r="K85" s="0"/>
-      <c r="L85" s="0"/>
-      <c r="M85" s="0"/>
-      <c r="N85" s="0"/>
-      <c r="O85" s="0"/>
-      <c r="P85" s="0"/>
-      <c r="Q85" s="0"/>
-      <c r="R85" s="0"/>
-      <c r="S85" s="0"/>
-      <c r="T85" s="0"/>
-      <c r="U85" s="0"/>
-      <c r="V85" s="0"/>
     </row>
     <row r="86">
       <c r="A86" s="0" t="s">
@@ -2749,7 +1722,7 @@
       </c>
       <c r="C86" s="0"/>
       <c r="D86" s="0" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E86" s="0"/>
       <c r="F86" s="0"/>
@@ -2757,18 +1730,6 @@
       <c r="H86" s="0"/>
       <c r="I86" s="0"/>
       <c r="J86" s="0"/>
-      <c r="K86" s="0"/>
-      <c r="L86" s="0"/>
-      <c r="M86" s="0"/>
-      <c r="N86" s="0"/>
-      <c r="O86" s="0"/>
-      <c r="P86" s="0"/>
-      <c r="Q86" s="0"/>
-      <c r="R86" s="0"/>
-      <c r="S86" s="0"/>
-      <c r="T86" s="0"/>
-      <c r="U86" s="0"/>
-      <c r="V86" s="0"/>
     </row>
     <row r="87">
       <c r="A87" s="0" t="s">
@@ -2779,7 +1740,7 @@
       </c>
       <c r="C87" s="0"/>
       <c r="D87" s="0" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E87" s="0"/>
       <c r="F87" s="0"/>
@@ -2787,18 +1748,6 @@
       <c r="H87" s="0"/>
       <c r="I87" s="0"/>
       <c r="J87" s="0"/>
-      <c r="K87" s="0"/>
-      <c r="L87" s="0"/>
-      <c r="M87" s="0"/>
-      <c r="N87" s="0"/>
-      <c r="O87" s="0"/>
-      <c r="P87" s="0"/>
-      <c r="Q87" s="0"/>
-      <c r="R87" s="0"/>
-      <c r="S87" s="0"/>
-      <c r="T87" s="0"/>
-      <c r="U87" s="0"/>
-      <c r="V87" s="0"/>
     </row>
     <row r="88">
       <c r="A88" s="0" t="s">
@@ -2809,7 +1758,7 @@
       </c>
       <c r="C88" s="0"/>
       <c r="D88" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E88" s="0"/>
       <c r="F88" s="0"/>
@@ -2817,18 +1766,6 @@
       <c r="H88" s="0"/>
       <c r="I88" s="0"/>
       <c r="J88" s="0"/>
-      <c r="K88" s="0"/>
-      <c r="L88" s="0"/>
-      <c r="M88" s="0"/>
-      <c r="N88" s="0"/>
-      <c r="O88" s="0"/>
-      <c r="P88" s="0"/>
-      <c r="Q88" s="0"/>
-      <c r="R88" s="0"/>
-      <c r="S88" s="0"/>
-      <c r="T88" s="0"/>
-      <c r="U88" s="0"/>
-      <c r="V88" s="0"/>
     </row>
     <row r="89">
       <c r="A89" s="0" t="s">
@@ -2839,7 +1776,7 @@
       </c>
       <c r="C89" s="0"/>
       <c r="D89" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E89" s="0"/>
       <c r="F89" s="0"/>
@@ -2847,18 +1784,6 @@
       <c r="H89" s="0"/>
       <c r="I89" s="0"/>
       <c r="J89" s="0"/>
-      <c r="K89" s="0"/>
-      <c r="L89" s="0"/>
-      <c r="M89" s="0"/>
-      <c r="N89" s="0"/>
-      <c r="O89" s="0"/>
-      <c r="P89" s="0"/>
-      <c r="Q89" s="0"/>
-      <c r="R89" s="0"/>
-      <c r="S89" s="0"/>
-      <c r="T89" s="0"/>
-      <c r="U89" s="0"/>
-      <c r="V89" s="0"/>
     </row>
     <row r="90">
       <c r="A90" s="0" t="s">
@@ -2869,7 +1794,7 @@
       </c>
       <c r="C90" s="0"/>
       <c r="D90" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E90" s="0"/>
       <c r="F90" s="0"/>
@@ -2877,18 +1802,6 @@
       <c r="H90" s="0"/>
       <c r="I90" s="0"/>
       <c r="J90" s="0"/>
-      <c r="K90" s="0"/>
-      <c r="L90" s="0"/>
-      <c r="M90" s="0"/>
-      <c r="N90" s="0"/>
-      <c r="O90" s="0"/>
-      <c r="P90" s="0"/>
-      <c r="Q90" s="0"/>
-      <c r="R90" s="0"/>
-      <c r="S90" s="0"/>
-      <c r="T90" s="0"/>
-      <c r="U90" s="0"/>
-      <c r="V90" s="0"/>
     </row>
     <row r="91">
       <c r="A91" s="0" t="s">
@@ -2899,7 +1812,7 @@
       </c>
       <c r="C91" s="0"/>
       <c r="D91" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E91" s="0"/>
       <c r="F91" s="0"/>
@@ -2907,18 +1820,6 @@
       <c r="H91" s="0"/>
       <c r="I91" s="0"/>
       <c r="J91" s="0"/>
-      <c r="K91" s="0"/>
-      <c r="L91" s="0"/>
-      <c r="M91" s="0"/>
-      <c r="N91" s="0"/>
-      <c r="O91" s="0"/>
-      <c r="P91" s="0"/>
-      <c r="Q91" s="0"/>
-      <c r="R91" s="0"/>
-      <c r="S91" s="0"/>
-      <c r="T91" s="0"/>
-      <c r="U91" s="0"/>
-      <c r="V91" s="0"/>
     </row>
     <row r="92">
       <c r="A92" s="0" t="s">
@@ -2929,7 +1830,7 @@
       </c>
       <c r="C92" s="0"/>
       <c r="D92" s="0" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E92" s="0"/>
       <c r="F92" s="0"/>
@@ -2937,18 +1838,6 @@
       <c r="H92" s="0"/>
       <c r="I92" s="0"/>
       <c r="J92" s="0"/>
-      <c r="K92" s="0"/>
-      <c r="L92" s="0"/>
-      <c r="M92" s="0"/>
-      <c r="N92" s="0"/>
-      <c r="O92" s="0"/>
-      <c r="P92" s="0"/>
-      <c r="Q92" s="0"/>
-      <c r="R92" s="0"/>
-      <c r="S92" s="0"/>
-      <c r="T92" s="0"/>
-      <c r="U92" s="0"/>
-      <c r="V92" s="0"/>
     </row>
     <row r="93">
       <c r="A93" s="0" t="s">
@@ -2959,7 +1848,7 @@
       </c>
       <c r="C93" s="0"/>
       <c r="D93" s="0" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E93" s="0"/>
       <c r="F93" s="0"/>
@@ -2967,18 +1856,6 @@
       <c r="H93" s="0"/>
       <c r="I93" s="0"/>
       <c r="J93" s="0"/>
-      <c r="K93" s="0"/>
-      <c r="L93" s="0"/>
-      <c r="M93" s="0"/>
-      <c r="N93" s="0"/>
-      <c r="O93" s="0"/>
-      <c r="P93" s="0"/>
-      <c r="Q93" s="0"/>
-      <c r="R93" s="0"/>
-      <c r="S93" s="0"/>
-      <c r="T93" s="0"/>
-      <c r="U93" s="0"/>
-      <c r="V93" s="0"/>
     </row>
     <row r="94">
       <c r="A94" s="0" t="s">
@@ -2993,18 +1870,6 @@
       <c r="H94" s="0"/>
       <c r="I94" s="0"/>
       <c r="J94" s="0"/>
-      <c r="K94" s="0"/>
-      <c r="L94" s="0"/>
-      <c r="M94" s="0"/>
-      <c r="N94" s="0"/>
-      <c r="O94" s="0"/>
-      <c r="P94" s="0"/>
-      <c r="Q94" s="0"/>
-      <c r="R94" s="0"/>
-      <c r="S94" s="0"/>
-      <c r="T94" s="0"/>
-      <c r="U94" s="0"/>
-      <c r="V94" s="0"/>
     </row>
     <row r="95">
       <c r="A95" s="0"/>
@@ -3017,18 +1882,6 @@
       <c r="H95" s="0"/>
       <c r="I95" s="0"/>
       <c r="J95" s="0"/>
-      <c r="K95" s="0"/>
-      <c r="L95" s="0"/>
-      <c r="M95" s="0"/>
-      <c r="N95" s="0"/>
-      <c r="O95" s="0"/>
-      <c r="P95" s="0"/>
-      <c r="Q95" s="0"/>
-      <c r="R95" s="0"/>
-      <c r="S95" s="0"/>
-      <c r="T95" s="0"/>
-      <c r="U95" s="0"/>
-      <c r="V95" s="0"/>
     </row>
     <row r="96">
       <c r="A96" s="0"/>
@@ -3041,18 +1894,6 @@
       <c r="H96" s="0"/>
       <c r="I96" s="0"/>
       <c r="J96" s="0"/>
-      <c r="K96" s="0"/>
-      <c r="L96" s="0"/>
-      <c r="M96" s="0"/>
-      <c r="N96" s="0"/>
-      <c r="O96" s="0"/>
-      <c r="P96" s="0"/>
-      <c r="Q96" s="0"/>
-      <c r="R96" s="0"/>
-      <c r="S96" s="0"/>
-      <c r="T96" s="0"/>
-      <c r="U96" s="0"/>
-      <c r="V96" s="0"/>
     </row>
     <row r="97">
       <c r="A97" s="0" t="s">
@@ -3067,18 +1908,6 @@
       <c r="H97" s="0"/>
       <c r="I97" s="0"/>
       <c r="J97" s="0"/>
-      <c r="K97" s="0"/>
-      <c r="L97" s="0"/>
-      <c r="M97" s="0"/>
-      <c r="N97" s="0"/>
-      <c r="O97" s="0"/>
-      <c r="P97" s="0"/>
-      <c r="Q97" s="0"/>
-      <c r="R97" s="0"/>
-      <c r="S97" s="0"/>
-      <c r="T97" s="0"/>
-      <c r="U97" s="0"/>
-      <c r="V97" s="0"/>
     </row>
     <row r="98">
       <c r="A98" s="0" t="s">
@@ -3095,18 +1924,6 @@
       <c r="H98" s="0"/>
       <c r="I98" s="0"/>
       <c r="J98" s="0"/>
-      <c r="K98" s="0"/>
-      <c r="L98" s="0"/>
-      <c r="M98" s="0"/>
-      <c r="N98" s="0"/>
-      <c r="O98" s="0"/>
-      <c r="P98" s="0"/>
-      <c r="Q98" s="0"/>
-      <c r="R98" s="0"/>
-      <c r="S98" s="0"/>
-      <c r="T98" s="0"/>
-      <c r="U98" s="0"/>
-      <c r="V98" s="0"/>
     </row>
     <row r="99">
       <c r="A99" s="0" t="s">
@@ -3123,24 +1940,12 @@
       <c r="H99" s="0"/>
       <c r="I99" s="0"/>
       <c r="J99" s="0"/>
-      <c r="K99" s="0"/>
-      <c r="L99" s="0"/>
-      <c r="M99" s="0"/>
-      <c r="N99" s="0"/>
-      <c r="O99" s="0"/>
-      <c r="P99" s="0"/>
-      <c r="Q99" s="0"/>
-      <c r="R99" s="0"/>
-      <c r="S99" s="0"/>
-      <c r="T99" s="0"/>
-      <c r="U99" s="0"/>
-      <c r="V99" s="0"/>
     </row>
     <row r="100">
       <c r="A100" s="0"/>
       <c r="B100" s="0"/>
       <c r="C100" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D100" s="0"/>
       <c r="E100" s="0"/>
@@ -3149,18 +1954,6 @@
       <c r="H100" s="0"/>
       <c r="I100" s="0"/>
       <c r="J100" s="0"/>
-      <c r="K100" s="0"/>
-      <c r="L100" s="0"/>
-      <c r="M100" s="0"/>
-      <c r="N100" s="0"/>
-      <c r="O100" s="0"/>
-      <c r="P100" s="0"/>
-      <c r="Q100" s="0"/>
-      <c r="R100" s="0"/>
-      <c r="S100" s="0"/>
-      <c r="T100" s="0"/>
-      <c r="U100" s="0"/>
-      <c r="V100" s="0"/>
     </row>
     <row r="101">
       <c r="A101" s="0" t="s">
@@ -3173,7 +1966,7 @@
         <v>0.25</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E101" s="0"/>
       <c r="F101" s="0"/>
@@ -3181,18 +1974,6 @@
       <c r="H101" s="0"/>
       <c r="I101" s="0"/>
       <c r="J101" s="0"/>
-      <c r="K101" s="0"/>
-      <c r="L101" s="0"/>
-      <c r="M101" s="0"/>
-      <c r="N101" s="0"/>
-      <c r="O101" s="0"/>
-      <c r="P101" s="0"/>
-      <c r="Q101" s="0"/>
-      <c r="R101" s="0"/>
-      <c r="S101" s="0"/>
-      <c r="T101" s="0"/>
-      <c r="U101" s="0"/>
-      <c r="V101" s="0"/>
     </row>
     <row r="102">
       <c r="A102" s="0" t="s">
@@ -3205,7 +1986,7 @@
         <v>70</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E102" s="0"/>
       <c r="F102" s="0"/>
@@ -3213,18 +1994,6 @@
       <c r="H102" s="0"/>
       <c r="I102" s="0"/>
       <c r="J102" s="0"/>
-      <c r="K102" s="0"/>
-      <c r="L102" s="0"/>
-      <c r="M102" s="0"/>
-      <c r="N102" s="0"/>
-      <c r="O102" s="0"/>
-      <c r="P102" s="0"/>
-      <c r="Q102" s="0"/>
-      <c r="R102" s="0"/>
-      <c r="S102" s="0"/>
-      <c r="T102" s="0"/>
-      <c r="U102" s="0"/>
-      <c r="V102" s="0"/>
     </row>
     <row r="103">
       <c r="A103" s="0" t="s">
@@ -3237,7 +2006,7 @@
         <v>1</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E103" s="0"/>
       <c r="F103" s="0"/>
@@ -3245,18 +2014,6 @@
       <c r="H103" s="0"/>
       <c r="I103" s="0"/>
       <c r="J103" s="0"/>
-      <c r="K103" s="0"/>
-      <c r="L103" s="0"/>
-      <c r="M103" s="0"/>
-      <c r="N103" s="0"/>
-      <c r="O103" s="0"/>
-      <c r="P103" s="0"/>
-      <c r="Q103" s="0"/>
-      <c r="R103" s="0"/>
-      <c r="S103" s="0"/>
-      <c r="T103" s="0"/>
-      <c r="U103" s="0"/>
-      <c r="V103" s="0"/>
     </row>
     <row r="104">
       <c r="A104" s="0" t="s">
@@ -3267,7 +2024,7 @@
       </c>
       <c r="C104" s="0"/>
       <c r="D104" s="0" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E104" s="0"/>
       <c r="F104" s="0"/>
@@ -3275,18 +2032,6 @@
       <c r="H104" s="0"/>
       <c r="I104" s="0"/>
       <c r="J104" s="0"/>
-      <c r="K104" s="0"/>
-      <c r="L104" s="0"/>
-      <c r="M104" s="0"/>
-      <c r="N104" s="0"/>
-      <c r="O104" s="0"/>
-      <c r="P104" s="0"/>
-      <c r="Q104" s="0"/>
-      <c r="R104" s="0"/>
-      <c r="S104" s="0"/>
-      <c r="T104" s="0"/>
-      <c r="U104" s="0"/>
-      <c r="V104" s="0"/>
     </row>
     <row r="105">
       <c r="A105" s="0" t="s">
@@ -3301,18 +2046,6 @@
       <c r="H105" s="0"/>
       <c r="I105" s="0"/>
       <c r="J105" s="0"/>
-      <c r="K105" s="0"/>
-      <c r="L105" s="0"/>
-      <c r="M105" s="0"/>
-      <c r="N105" s="0"/>
-      <c r="O105" s="0"/>
-      <c r="P105" s="0"/>
-      <c r="Q105" s="0"/>
-      <c r="R105" s="0"/>
-      <c r="S105" s="0"/>
-      <c r="T105" s="0"/>
-      <c r="U105" s="0"/>
-      <c r="V105" s="0"/>
     </row>
     <row r="106">
       <c r="A106" s="0"/>
@@ -3325,18 +2058,6 @@
       <c r="H106" s="0"/>
       <c r="I106" s="0"/>
       <c r="J106" s="0"/>
-      <c r="K106" s="0"/>
-      <c r="L106" s="0"/>
-      <c r="M106" s="0"/>
-      <c r="N106" s="0"/>
-      <c r="O106" s="0"/>
-      <c r="P106" s="0"/>
-      <c r="Q106" s="0"/>
-      <c r="R106" s="0"/>
-      <c r="S106" s="0"/>
-      <c r="T106" s="0"/>
-      <c r="U106" s="0"/>
-      <c r="V106" s="0"/>
     </row>
     <row r="107">
       <c r="A107" s="0"/>
@@ -3349,18 +2070,6 @@
       <c r="H107" s="0"/>
       <c r="I107" s="0"/>
       <c r="J107" s="0"/>
-      <c r="K107" s="0"/>
-      <c r="L107" s="0"/>
-      <c r="M107" s="0"/>
-      <c r="N107" s="0"/>
-      <c r="O107" s="0"/>
-      <c r="P107" s="0"/>
-      <c r="Q107" s="0"/>
-      <c r="R107" s="0"/>
-      <c r="S107" s="0"/>
-      <c r="T107" s="0"/>
-      <c r="U107" s="0"/>
-      <c r="V107" s="0"/>
     </row>
     <row r="108">
       <c r="A108" s="0" t="s">
@@ -3375,18 +2084,6 @@
       <c r="H108" s="0"/>
       <c r="I108" s="0"/>
       <c r="J108" s="0"/>
-      <c r="K108" s="0"/>
-      <c r="L108" s="0"/>
-      <c r="M108" s="0"/>
-      <c r="N108" s="0"/>
-      <c r="O108" s="0"/>
-      <c r="P108" s="0"/>
-      <c r="Q108" s="0"/>
-      <c r="R108" s="0"/>
-      <c r="S108" s="0"/>
-      <c r="T108" s="0"/>
-      <c r="U108" s="0"/>
-      <c r="V108" s="0"/>
     </row>
     <row r="109">
       <c r="A109" s="0" t="s">
@@ -3403,18 +2100,6 @@
       <c r="H109" s="0"/>
       <c r="I109" s="0"/>
       <c r="J109" s="0"/>
-      <c r="K109" s="0"/>
-      <c r="L109" s="0"/>
-      <c r="M109" s="0"/>
-      <c r="N109" s="0"/>
-      <c r="O109" s="0"/>
-      <c r="P109" s="0"/>
-      <c r="Q109" s="0"/>
-      <c r="R109" s="0"/>
-      <c r="S109" s="0"/>
-      <c r="T109" s="0"/>
-      <c r="U109" s="0"/>
-      <c r="V109" s="0"/>
     </row>
     <row r="110">
       <c r="A110" s="0" t="s">
@@ -3431,18 +2116,6 @@
       <c r="H110" s="0"/>
       <c r="I110" s="0"/>
       <c r="J110" s="0"/>
-      <c r="K110" s="0"/>
-      <c r="L110" s="0"/>
-      <c r="M110" s="0"/>
-      <c r="N110" s="0"/>
-      <c r="O110" s="0"/>
-      <c r="P110" s="0"/>
-      <c r="Q110" s="0"/>
-      <c r="R110" s="0"/>
-      <c r="S110" s="0"/>
-      <c r="T110" s="0"/>
-      <c r="U110" s="0"/>
-      <c r="V110" s="0"/>
     </row>
     <row r="111">
       <c r="A111" s="0" t="s">
@@ -3452,37 +2125,25 @@
         <v>63</v>
       </c>
       <c r="C111" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D111" s="0" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E111" s="0" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F111" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G111" s="0" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H111" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I111" s="0"/>
       <c r="J111" s="0"/>
-      <c r="K111" s="0"/>
-      <c r="L111" s="0"/>
-      <c r="M111" s="0"/>
-      <c r="N111" s="0"/>
-      <c r="O111" s="0"/>
-      <c r="P111" s="0"/>
-      <c r="Q111" s="0"/>
-      <c r="R111" s="0"/>
-      <c r="S111" s="0"/>
-      <c r="T111" s="0"/>
-      <c r="U111" s="0"/>
-      <c r="V111" s="0"/>
     </row>
     <row r="112">
       <c r="A112" s="0" t="s">
@@ -3499,18 +2160,6 @@
       <c r="H112" s="0"/>
       <c r="I112" s="0"/>
       <c r="J112" s="0"/>
-      <c r="K112" s="0"/>
-      <c r="L112" s="0"/>
-      <c r="M112" s="0"/>
-      <c r="N112" s="0"/>
-      <c r="O112" s="0"/>
-      <c r="P112" s="0"/>
-      <c r="Q112" s="0"/>
-      <c r="R112" s="0"/>
-      <c r="S112" s="0"/>
-      <c r="T112" s="0"/>
-      <c r="U112" s="0"/>
-      <c r="V112" s="0"/>
     </row>
     <row r="113">
       <c r="A113" s="0" t="s">
@@ -3527,18 +2176,6 @@
       <c r="H113" s="0"/>
       <c r="I113" s="0"/>
       <c r="J113" s="0"/>
-      <c r="K113" s="0"/>
-      <c r="L113" s="0"/>
-      <c r="M113" s="0"/>
-      <c r="N113" s="0"/>
-      <c r="O113" s="0"/>
-      <c r="P113" s="0"/>
-      <c r="Q113" s="0"/>
-      <c r="R113" s="0"/>
-      <c r="S113" s="0"/>
-      <c r="T113" s="0"/>
-      <c r="U113" s="0"/>
-      <c r="V113" s="0"/>
     </row>
     <row r="114">
       <c r="A114" s="0" t="s">
@@ -3555,18 +2192,6 @@
       <c r="H114" s="0"/>
       <c r="I114" s="0"/>
       <c r="J114" s="0"/>
-      <c r="K114" s="0"/>
-      <c r="L114" s="0"/>
-      <c r="M114" s="0"/>
-      <c r="N114" s="0"/>
-      <c r="O114" s="0"/>
-      <c r="P114" s="0"/>
-      <c r="Q114" s="0"/>
-      <c r="R114" s="0"/>
-      <c r="S114" s="0"/>
-      <c r="T114" s="0"/>
-      <c r="U114" s="0"/>
-      <c r="V114" s="0"/>
     </row>
     <row r="115">
       <c r="A115" s="0" t="s">
@@ -3583,18 +2208,6 @@
       <c r="H115" s="0"/>
       <c r="I115" s="0"/>
       <c r="J115" s="0"/>
-      <c r="K115" s="0"/>
-      <c r="L115" s="0"/>
-      <c r="M115" s="0"/>
-      <c r="N115" s="0"/>
-      <c r="O115" s="0"/>
-      <c r="P115" s="0"/>
-      <c r="Q115" s="0"/>
-      <c r="R115" s="0"/>
-      <c r="S115" s="0"/>
-      <c r="T115" s="0"/>
-      <c r="U115" s="0"/>
-      <c r="V115" s="0"/>
     </row>
     <row r="116">
       <c r="A116" s="0" t="s">
@@ -3611,18 +2224,6 @@
       <c r="H116" s="0"/>
       <c r="I116" s="0"/>
       <c r="J116" s="0"/>
-      <c r="K116" s="0"/>
-      <c r="L116" s="0"/>
-      <c r="M116" s="0"/>
-      <c r="N116" s="0"/>
-      <c r="O116" s="0"/>
-      <c r="P116" s="0"/>
-      <c r="Q116" s="0"/>
-      <c r="R116" s="0"/>
-      <c r="S116" s="0"/>
-      <c r="T116" s="0"/>
-      <c r="U116" s="0"/>
-      <c r="V116" s="0"/>
     </row>
     <row r="117">
       <c r="A117" s="0" t="s">
@@ -3639,18 +2240,6 @@
       <c r="H117" s="0"/>
       <c r="I117" s="0"/>
       <c r="J117" s="0"/>
-      <c r="K117" s="0"/>
-      <c r="L117" s="0"/>
-      <c r="M117" s="0"/>
-      <c r="N117" s="0"/>
-      <c r="O117" s="0"/>
-      <c r="P117" s="0"/>
-      <c r="Q117" s="0"/>
-      <c r="R117" s="0"/>
-      <c r="S117" s="0"/>
-      <c r="T117" s="0"/>
-      <c r="U117" s="0"/>
-      <c r="V117" s="0"/>
     </row>
     <row r="118">
       <c r="A118" s="0" t="s">
@@ -3667,18 +2256,6 @@
       <c r="H118" s="0"/>
       <c r="I118" s="0"/>
       <c r="J118" s="0"/>
-      <c r="K118" s="0"/>
-      <c r="L118" s="0"/>
-      <c r="M118" s="0"/>
-      <c r="N118" s="0"/>
-      <c r="O118" s="0"/>
-      <c r="P118" s="0"/>
-      <c r="Q118" s="0"/>
-      <c r="R118" s="0"/>
-      <c r="S118" s="0"/>
-      <c r="T118" s="0"/>
-      <c r="U118" s="0"/>
-      <c r="V118" s="0"/>
     </row>
     <row r="119">
       <c r="A119" s="0" t="s">
@@ -3693,18 +2270,6 @@
       <c r="H119" s="0"/>
       <c r="I119" s="0"/>
       <c r="J119" s="0"/>
-      <c r="K119" s="0"/>
-      <c r="L119" s="0"/>
-      <c r="M119" s="0"/>
-      <c r="N119" s="0"/>
-      <c r="O119" s="0"/>
-      <c r="P119" s="0"/>
-      <c r="Q119" s="0"/>
-      <c r="R119" s="0"/>
-      <c r="S119" s="0"/>
-      <c r="T119" s="0"/>
-      <c r="U119" s="0"/>
-      <c r="V119" s="0"/>
     </row>
     <row r="120">
       <c r="A120" s="0"/>
@@ -3717,18 +2282,6 @@
       <c r="H120" s="0"/>
       <c r="I120" s="0"/>
       <c r="J120" s="0"/>
-      <c r="K120" s="0"/>
-      <c r="L120" s="0"/>
-      <c r="M120" s="0"/>
-      <c r="N120" s="0"/>
-      <c r="O120" s="0"/>
-      <c r="P120" s="0"/>
-      <c r="Q120" s="0"/>
-      <c r="R120" s="0"/>
-      <c r="S120" s="0"/>
-      <c r="T120" s="0"/>
-      <c r="U120" s="0"/>
-      <c r="V120" s="0"/>
     </row>
     <row r="121">
       <c r="A121" s="0"/>
@@ -3741,18 +2294,6 @@
       <c r="H121" s="0"/>
       <c r="I121" s="0"/>
       <c r="J121" s="0"/>
-      <c r="K121" s="0"/>
-      <c r="L121" s="0"/>
-      <c r="M121" s="0"/>
-      <c r="N121" s="0"/>
-      <c r="O121" s="0"/>
-      <c r="P121" s="0"/>
-      <c r="Q121" s="0"/>
-      <c r="R121" s="0"/>
-      <c r="S121" s="0"/>
-      <c r="T121" s="0"/>
-      <c r="U121" s="0"/>
-      <c r="V121" s="0"/>
     </row>
   </sheetData>
 </worksheet>

--- a/CryoGrid/CryoGridCommunity_results/templates/automatic_loops/loop1/loop1.xlsx
+++ b/CryoGrid/CryoGridCommunity_results/templates/automatic_loops/loop1/loop1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="183" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="181" uniqueCount="95">
   <si>
     <t>-------------------</t>
   </si>
@@ -211,7 +211,7 @@
     <t>restart_OUT_last_timestep</t>
   </si>
   <si>
-    <t>D:\Utilisateurs\pozsgayv\Documents\CryoGrid_VP_Workflow\CryoGrid\CryoGridCommunity_results\templates\automatic_loops\loop1\</t>
+    <t>..\CryoGridCommunity_results\templates\automatic_loops\loop1\</t>
   </si>
   <si>
     <t>automatic_loops_loop1_last_timestep</t>
@@ -238,9 +238,6 @@
     <t>snow_all</t>
   </si>
   <si>
-    <t>D:\Utilisateurs\pozsgayv\Documents\CryoGrid_VP_Workflow\forcing\Forcing_Data\</t>
-  </si>
-  <si>
     <t>default value</t>
   </si>
   <si>
@@ -254,9 +251,6 @@
   </si>
   <si>
     <t>timestep that model progress is displayed [days]</t>
-  </si>
-  <si>
-    <t>same as OUT_TwaterIce, but you can set elevations relative to the surface elevation, which is much more user-friendly</t>
   </si>
   <si>
     <t>water</t>
@@ -354,8 +348,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.453125" customWidth="true"/>
-    <col min="2" max="2" width="114.7265625" customWidth="true"/>
-    <col min="3" max="3" width="71.08984375" customWidth="true"/>
+    <col min="2" max="2" width="56.54296875" customWidth="true"/>
+    <col min="3" max="3" width="21.90625" customWidth="true"/>
     <col min="4" max="4" width="118.7265625" customWidth="true"/>
     <col min="5" max="5" width="12.90625" customWidth="true"/>
     <col min="6" max="6" width="8.08984375" customWidth="true"/>
@@ -457,7 +451,7 @@
         <v>20</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F6" s="0"/>
       <c r="G6" s="0"/>
@@ -479,7 +473,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F7" s="0"/>
       <c r="G7" s="0"/>
@@ -501,7 +495,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F8" s="0"/>
       <c r="G8" s="0"/>
@@ -874,7 +868,7 @@
         <v>46</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E33" s="0"/>
       <c r="F33" s="0"/>
@@ -894,7 +888,7 @@
         <v>1</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E34" s="0"/>
       <c r="F34" s="0"/>
@@ -1092,7 +1086,7 @@
         <v>59</v>
       </c>
       <c r="F47" s="0" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G47" s="0"/>
       <c r="H47" s="0"/>
@@ -1116,7 +1110,7 @@
         <v>1</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G48" s="0"/>
       <c r="H48" s="0"/>
@@ -1230,9 +1224,7 @@
       <c r="B56" s="0" t="s">
         <v>69</v>
       </c>
-      <c r="C56" s="0" t="s">
-        <v>74</v>
-      </c>
+      <c r="C56" s="0"/>
       <c r="D56" s="0"/>
       <c r="E56" s="0"/>
       <c r="F56" s="0"/>
@@ -1258,7 +1250,7 @@
         <v>1</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G57" s="0"/>
       <c r="H57" s="0"/>
@@ -1282,7 +1274,7 @@
         <v>2</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G58" s="0"/>
       <c r="H58" s="0"/>
@@ -1364,7 +1356,7 @@
         <v>43</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E63" s="0"/>
       <c r="F63" s="0"/>
@@ -1384,7 +1376,7 @@
         <v>1</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E64" s="0"/>
       <c r="F64" s="0"/>
@@ -1555,7 +1547,7 @@
       <c r="A76" s="0"/>
       <c r="B76" s="0"/>
       <c r="C76" s="0" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D76" s="0"/>
       <c r="E76" s="0"/>
@@ -1576,7 +1568,7 @@
         <v>5</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E77" s="0"/>
       <c r="F77" s="0"/>
@@ -1661,9 +1653,7 @@
         <v>1</v>
       </c>
       <c r="C83" s="0"/>
-      <c r="D83" s="0" t="s">
-        <v>80</v>
-      </c>
+      <c r="D83" s="0"/>
       <c r="E83" s="0"/>
       <c r="F83" s="0"/>
       <c r="G83" s="0"/>
@@ -1675,7 +1665,7 @@
       <c r="A84" s="0"/>
       <c r="B84" s="0"/>
       <c r="C84" s="0" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D84" s="0"/>
       <c r="E84" s="0"/>
@@ -1693,22 +1683,22 @@
         <v>63</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E85" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="F85" s="0" t="s">
         <v>91</v>
       </c>
-      <c r="F85" s="0" t="s">
+      <c r="G85" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="H85" s="0" t="s">
         <v>93</v>
-      </c>
-      <c r="G85" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="H85" s="0" t="s">
-        <v>95</v>
       </c>
       <c r="I85" s="0"/>
       <c r="J85" s="0"/>
@@ -1722,7 +1712,7 @@
       </c>
       <c r="C86" s="0"/>
       <c r="D86" s="0" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E86" s="0"/>
       <c r="F86" s="0"/>
@@ -1740,7 +1730,7 @@
       </c>
       <c r="C87" s="0"/>
       <c r="D87" s="0" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E87" s="0"/>
       <c r="F87" s="0"/>
@@ -1758,7 +1748,7 @@
       </c>
       <c r="C88" s="0"/>
       <c r="D88" s="0" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E88" s="0"/>
       <c r="F88" s="0"/>
@@ -1776,7 +1766,7 @@
       </c>
       <c r="C89" s="0"/>
       <c r="D89" s="0" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E89" s="0"/>
       <c r="F89" s="0"/>
@@ -1794,7 +1784,7 @@
       </c>
       <c r="C90" s="0"/>
       <c r="D90" s="0" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E90" s="0"/>
       <c r="F90" s="0"/>
@@ -1812,7 +1802,7 @@
       </c>
       <c r="C91" s="0"/>
       <c r="D91" s="0" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E91" s="0"/>
       <c r="F91" s="0"/>
@@ -1830,7 +1820,7 @@
       </c>
       <c r="C92" s="0"/>
       <c r="D92" s="0" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E92" s="0"/>
       <c r="F92" s="0"/>
@@ -1848,7 +1838,7 @@
       </c>
       <c r="C93" s="0"/>
       <c r="D93" s="0" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E93" s="0"/>
       <c r="F93" s="0"/>
@@ -1945,7 +1935,7 @@
       <c r="A100" s="0"/>
       <c r="B100" s="0"/>
       <c r="C100" s="0" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D100" s="0"/>
       <c r="E100" s="0"/>
@@ -1966,7 +1956,7 @@
         <v>0.25</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E101" s="0"/>
       <c r="F101" s="0"/>
@@ -1986,7 +1976,7 @@
         <v>70</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E102" s="0"/>
       <c r="F102" s="0"/>
@@ -2006,7 +1996,7 @@
         <v>1</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E103" s="0"/>
       <c r="F103" s="0"/>
@@ -2024,7 +2014,7 @@
       </c>
       <c r="C104" s="0"/>
       <c r="D104" s="0" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E104" s="0"/>
       <c r="F104" s="0"/>
@@ -2125,22 +2115,22 @@
         <v>63</v>
       </c>
       <c r="C111" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="D111" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="E111" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="F111" s="0" t="s">
         <v>77</v>
       </c>
-      <c r="D111" s="0" t="s">
-        <v>90</v>
-      </c>
-      <c r="E111" s="0" t="s">
+      <c r="G111" s="0" t="s">
         <v>92</v>
       </c>
-      <c r="F111" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="G111" s="0" t="s">
+      <c r="H111" s="0" t="s">
         <v>94</v>
-      </c>
-      <c r="H111" s="0" t="s">
-        <v>96</v>
       </c>
       <c r="I111" s="0"/>
       <c r="J111" s="0"/>

--- a/CryoGrid/CryoGridCommunity_results/templates/automatic_loops/loop1/loop1.xlsx
+++ b/CryoGrid/CryoGridCommunity_results/templates/automatic_loops/loop1/loop1.xlsx
@@ -344,7 +344,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J121"/>
+  <dimension ref="A1:L121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.453125" customWidth="true"/>
@@ -357,6 +357,8 @@
     <col min="8" max="8" width="78.81640625" customWidth="true"/>
     <col min="9" max="9" width="9.140625"/>
     <col min="10" max="10" width="9.140625"/>
+    <col min="11" max="11" width="9.140625"/>
+    <col min="12" max="12" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -372,6 +374,8 @@
       <c r="H1" s="0"/>
       <c r="I1" s="0"/>
       <c r="J1" s="0"/>
+      <c r="K1" s="0"/>
+      <c r="L1" s="0"/>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
@@ -388,6 +392,8 @@
       <c r="H2" s="0"/>
       <c r="I2" s="0"/>
       <c r="J2" s="0"/>
+      <c r="K2" s="0"/>
+      <c r="L2" s="0"/>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
@@ -404,6 +410,8 @@
       <c r="H3" s="0"/>
       <c r="I3" s="0"/>
       <c r="J3" s="0"/>
+      <c r="K3" s="0"/>
+      <c r="L3" s="0"/>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
@@ -420,6 +428,8 @@
       <c r="H4" s="0"/>
       <c r="I4" s="0"/>
       <c r="J4" s="0"/>
+      <c r="K4" s="0"/>
+      <c r="L4" s="0"/>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
@@ -436,6 +446,8 @@
       <c r="H5" s="0"/>
       <c r="I5" s="0"/>
       <c r="J5" s="0"/>
+      <c r="K5" s="0"/>
+      <c r="L5" s="0"/>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
@@ -458,6 +470,8 @@
       <c r="H6" s="0"/>
       <c r="I6" s="0"/>
       <c r="J6" s="0"/>
+      <c r="K6" s="0"/>
+      <c r="L6" s="0"/>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
@@ -480,6 +494,8 @@
       <c r="H7" s="0"/>
       <c r="I7" s="0"/>
       <c r="J7" s="0"/>
+      <c r="K7" s="0"/>
+      <c r="L7" s="0"/>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
@@ -502,6 +518,8 @@
       <c r="H8" s="0"/>
       <c r="I8" s="0"/>
       <c r="J8" s="0"/>
+      <c r="K8" s="0"/>
+      <c r="L8" s="0"/>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
@@ -516,6 +534,8 @@
       <c r="H9" s="0"/>
       <c r="I9" s="0"/>
       <c r="J9" s="0"/>
+      <c r="K9" s="0"/>
+      <c r="L9" s="0"/>
     </row>
     <row r="10">
       <c r="A10" s="0"/>
@@ -528,6 +548,8 @@
       <c r="H10" s="0"/>
       <c r="I10" s="0"/>
       <c r="J10" s="0"/>
+      <c r="K10" s="0"/>
+      <c r="L10" s="0"/>
     </row>
     <row r="11">
       <c r="A11" s="0"/>
@@ -540,6 +562,8 @@
       <c r="H11" s="0"/>
       <c r="I11" s="0"/>
       <c r="J11" s="0"/>
+      <c r="K11" s="0"/>
+      <c r="L11" s="0"/>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
@@ -554,6 +578,8 @@
       <c r="H12" s="0"/>
       <c r="I12" s="0"/>
       <c r="J12" s="0"/>
+      <c r="K12" s="0"/>
+      <c r="L12" s="0"/>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
@@ -570,6 +596,8 @@
       <c r="H13" s="0"/>
       <c r="I13" s="0"/>
       <c r="J13" s="0"/>
+      <c r="K13" s="0"/>
+      <c r="L13" s="0"/>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
@@ -586,6 +614,8 @@
       <c r="H14" s="0"/>
       <c r="I14" s="0"/>
       <c r="J14" s="0"/>
+      <c r="K14" s="0"/>
+      <c r="L14" s="0"/>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
@@ -602,6 +632,8 @@
       <c r="H15" s="0"/>
       <c r="I15" s="0"/>
       <c r="J15" s="0"/>
+      <c r="K15" s="0"/>
+      <c r="L15" s="0"/>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
@@ -618,6 +650,8 @@
       <c r="H16" s="0"/>
       <c r="I16" s="0"/>
       <c r="J16" s="0"/>
+      <c r="K16" s="0"/>
+      <c r="L16" s="0"/>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
@@ -634,6 +668,8 @@
       <c r="H17" s="0"/>
       <c r="I17" s="0"/>
       <c r="J17" s="0"/>
+      <c r="K17" s="0"/>
+      <c r="L17" s="0"/>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
@@ -650,6 +686,8 @@
       <c r="H18" s="0"/>
       <c r="I18" s="0"/>
       <c r="J18" s="0"/>
+      <c r="K18" s="0"/>
+      <c r="L18" s="0"/>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
@@ -666,6 +704,8 @@
       <c r="H19" s="0"/>
       <c r="I19" s="0"/>
       <c r="J19" s="0"/>
+      <c r="K19" s="0"/>
+      <c r="L19" s="0"/>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
@@ -682,6 +722,8 @@
       <c r="H20" s="0"/>
       <c r="I20" s="0"/>
       <c r="J20" s="0"/>
+      <c r="K20" s="0"/>
+      <c r="L20" s="0"/>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
@@ -698,6 +740,8 @@
       <c r="H21" s="0"/>
       <c r="I21" s="0"/>
       <c r="J21" s="0"/>
+      <c r="K21" s="0"/>
+      <c r="L21" s="0"/>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
@@ -712,6 +756,8 @@
       <c r="H22" s="0"/>
       <c r="I22" s="0"/>
       <c r="J22" s="0"/>
+      <c r="K22" s="0"/>
+      <c r="L22" s="0"/>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
@@ -726,6 +772,8 @@
       <c r="H23" s="0"/>
       <c r="I23" s="0"/>
       <c r="J23" s="0"/>
+      <c r="K23" s="0"/>
+      <c r="L23" s="0"/>
     </row>
     <row r="24">
       <c r="A24" s="0"/>
@@ -738,6 +786,8 @@
       <c r="H24" s="0"/>
       <c r="I24" s="0"/>
       <c r="J24" s="0"/>
+      <c r="K24" s="0"/>
+      <c r="L24" s="0"/>
     </row>
     <row r="25">
       <c r="A25" s="0"/>
@@ -750,6 +800,8 @@
       <c r="H25" s="0"/>
       <c r="I25" s="0"/>
       <c r="J25" s="0"/>
+      <c r="K25" s="0"/>
+      <c r="L25" s="0"/>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
@@ -764,6 +816,8 @@
       <c r="H26" s="0"/>
       <c r="I26" s="0"/>
       <c r="J26" s="0"/>
+      <c r="K26" s="0"/>
+      <c r="L26" s="0"/>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
@@ -780,6 +834,8 @@
       <c r="H27" s="0"/>
       <c r="I27" s="0"/>
       <c r="J27" s="0"/>
+      <c r="K27" s="0"/>
+      <c r="L27" s="0"/>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
@@ -796,6 +852,8 @@
       <c r="H28" s="0"/>
       <c r="I28" s="0"/>
       <c r="J28" s="0"/>
+      <c r="K28" s="0"/>
+      <c r="L28" s="0"/>
     </row>
     <row r="29">
       <c r="A29" s="0"/>
@@ -808,6 +866,8 @@
       <c r="H29" s="0"/>
       <c r="I29" s="0"/>
       <c r="J29" s="0"/>
+      <c r="K29" s="0"/>
+      <c r="L29" s="0"/>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
@@ -824,6 +884,8 @@
       <c r="H30" s="0"/>
       <c r="I30" s="0"/>
       <c r="J30" s="0"/>
+      <c r="K30" s="0"/>
+      <c r="L30" s="0"/>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
@@ -840,6 +902,8 @@
       <c r="H31" s="0"/>
       <c r="I31" s="0"/>
       <c r="J31" s="0"/>
+      <c r="K31" s="0"/>
+      <c r="L31" s="0"/>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
@@ -856,6 +920,8 @@
       <c r="H32" s="0"/>
       <c r="I32" s="0"/>
       <c r="J32" s="0"/>
+      <c r="K32" s="0"/>
+      <c r="L32" s="0"/>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
@@ -876,6 +942,8 @@
       <c r="H33" s="0"/>
       <c r="I33" s="0"/>
       <c r="J33" s="0"/>
+      <c r="K33" s="0"/>
+      <c r="L33" s="0"/>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
@@ -896,6 +964,8 @@
       <c r="H34" s="0"/>
       <c r="I34" s="0"/>
       <c r="J34" s="0"/>
+      <c r="K34" s="0"/>
+      <c r="L34" s="0"/>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
@@ -910,6 +980,8 @@
       <c r="H35" s="0"/>
       <c r="I35" s="0"/>
       <c r="J35" s="0"/>
+      <c r="K35" s="0"/>
+      <c r="L35" s="0"/>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
@@ -924,6 +996,8 @@
       <c r="H36" s="0"/>
       <c r="I36" s="0"/>
       <c r="J36" s="0"/>
+      <c r="K36" s="0"/>
+      <c r="L36" s="0"/>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
@@ -938,6 +1012,8 @@
       <c r="H37" s="0"/>
       <c r="I37" s="0"/>
       <c r="J37" s="0"/>
+      <c r="K37" s="0"/>
+      <c r="L37" s="0"/>
     </row>
     <row r="38">
       <c r="A38" s="0"/>
@@ -950,6 +1026,8 @@
       <c r="H38" s="0"/>
       <c r="I38" s="0"/>
       <c r="J38" s="0"/>
+      <c r="K38" s="0"/>
+      <c r="L38" s="0"/>
     </row>
     <row r="39">
       <c r="A39" s="0"/>
@@ -962,6 +1040,8 @@
       <c r="H39" s="0"/>
       <c r="I39" s="0"/>
       <c r="J39" s="0"/>
+      <c r="K39" s="0"/>
+      <c r="L39" s="0"/>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
@@ -976,6 +1056,8 @@
       <c r="H40" s="0"/>
       <c r="I40" s="0"/>
       <c r="J40" s="0"/>
+      <c r="K40" s="0"/>
+      <c r="L40" s="0"/>
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
@@ -992,6 +1074,8 @@
       <c r="H41" s="0"/>
       <c r="I41" s="0"/>
       <c r="J41" s="0"/>
+      <c r="K41" s="0"/>
+      <c r="L41" s="0"/>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
@@ -1008,6 +1092,8 @@
       <c r="H42" s="0"/>
       <c r="I42" s="0"/>
       <c r="J42" s="0"/>
+      <c r="K42" s="0"/>
+      <c r="L42" s="0"/>
     </row>
     <row r="43">
       <c r="A43" s="0"/>
@@ -1020,6 +1106,8 @@
       <c r="H43" s="0"/>
       <c r="I43" s="0"/>
       <c r="J43" s="0"/>
+      <c r="K43" s="0"/>
+      <c r="L43" s="0"/>
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
@@ -1036,6 +1124,8 @@
       <c r="H44" s="0"/>
       <c r="I44" s="0"/>
       <c r="J44" s="0"/>
+      <c r="K44" s="0"/>
+      <c r="L44" s="0"/>
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
@@ -1052,6 +1142,8 @@
       <c r="H45" s="0"/>
       <c r="I45" s="0"/>
       <c r="J45" s="0"/>
+      <c r="K45" s="0"/>
+      <c r="L45" s="0"/>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
@@ -1068,6 +1160,8 @@
       <c r="H46" s="0"/>
       <c r="I46" s="0"/>
       <c r="J46" s="0"/>
+      <c r="K46" s="0"/>
+      <c r="L46" s="0"/>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
@@ -1092,6 +1186,8 @@
       <c r="H47" s="0"/>
       <c r="I47" s="0"/>
       <c r="J47" s="0"/>
+      <c r="K47" s="0"/>
+      <c r="L47" s="0"/>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
@@ -1116,6 +1212,8 @@
       <c r="H48" s="0"/>
       <c r="I48" s="0"/>
       <c r="J48" s="0"/>
+      <c r="K48" s="0"/>
+      <c r="L48" s="0"/>
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
@@ -1130,6 +1228,8 @@
       <c r="H49" s="0"/>
       <c r="I49" s="0"/>
       <c r="J49" s="0"/>
+      <c r="K49" s="0"/>
+      <c r="L49" s="0"/>
     </row>
     <row r="50">
       <c r="A50" s="0"/>
@@ -1142,6 +1242,8 @@
       <c r="H50" s="0"/>
       <c r="I50" s="0"/>
       <c r="J50" s="0"/>
+      <c r="K50" s="0"/>
+      <c r="L50" s="0"/>
     </row>
     <row r="51">
       <c r="A51" s="0"/>
@@ -1154,6 +1256,8 @@
       <c r="H51" s="0"/>
       <c r="I51" s="0"/>
       <c r="J51" s="0"/>
+      <c r="K51" s="0"/>
+      <c r="L51" s="0"/>
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
@@ -1168,6 +1272,8 @@
       <c r="H52" s="0"/>
       <c r="I52" s="0"/>
       <c r="J52" s="0"/>
+      <c r="K52" s="0"/>
+      <c r="L52" s="0"/>
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
@@ -1184,6 +1290,8 @@
       <c r="H53" s="0"/>
       <c r="I53" s="0"/>
       <c r="J53" s="0"/>
+      <c r="K53" s="0"/>
+      <c r="L53" s="0"/>
     </row>
     <row r="54">
       <c r="A54" s="0" t="s">
@@ -1200,6 +1308,8 @@
       <c r="H54" s="0"/>
       <c r="I54" s="0"/>
       <c r="J54" s="0"/>
+      <c r="K54" s="0"/>
+      <c r="L54" s="0"/>
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
@@ -1216,6 +1326,8 @@
       <c r="H55" s="0"/>
       <c r="I55" s="0"/>
       <c r="J55" s="0"/>
+      <c r="K55" s="0"/>
+      <c r="L55" s="0"/>
     </row>
     <row r="56">
       <c r="A56" s="0" t="s">
@@ -1232,6 +1344,8 @@
       <c r="H56" s="0"/>
       <c r="I56" s="0"/>
       <c r="J56" s="0"/>
+      <c r="K56" s="0"/>
+      <c r="L56" s="0"/>
     </row>
     <row r="57">
       <c r="A57" s="0" t="s">
@@ -1256,6 +1370,8 @@
       <c r="H57" s="0"/>
       <c r="I57" s="0"/>
       <c r="J57" s="0"/>
+      <c r="K57" s="0"/>
+      <c r="L57" s="0"/>
     </row>
     <row r="58">
       <c r="A58" s="0" t="s">
@@ -1280,6 +1396,8 @@
       <c r="H58" s="0"/>
       <c r="I58" s="0"/>
       <c r="J58" s="0"/>
+      <c r="K58" s="0"/>
+      <c r="L58" s="0"/>
     </row>
     <row r="59">
       <c r="A59" s="0" t="s">
@@ -1296,6 +1414,8 @@
       <c r="H59" s="0"/>
       <c r="I59" s="0"/>
       <c r="J59" s="0"/>
+      <c r="K59" s="0"/>
+      <c r="L59" s="0"/>
     </row>
     <row r="60">
       <c r="A60" s="0" t="s">
@@ -1312,6 +1432,8 @@
       <c r="H60" s="0"/>
       <c r="I60" s="0"/>
       <c r="J60" s="0"/>
+      <c r="K60" s="0"/>
+      <c r="L60" s="0"/>
     </row>
     <row r="61">
       <c r="A61" s="0" t="s">
@@ -1328,6 +1450,8 @@
       <c r="H61" s="0"/>
       <c r="I61" s="0"/>
       <c r="J61" s="0"/>
+      <c r="K61" s="0"/>
+      <c r="L61" s="0"/>
     </row>
     <row r="62">
       <c r="A62" s="0" t="s">
@@ -1344,6 +1468,8 @@
       <c r="H62" s="0"/>
       <c r="I62" s="0"/>
       <c r="J62" s="0"/>
+      <c r="K62" s="0"/>
+      <c r="L62" s="0"/>
     </row>
     <row r="63">
       <c r="A63" s="0" t="s">
@@ -1364,6 +1490,8 @@
       <c r="H63" s="0"/>
       <c r="I63" s="0"/>
       <c r="J63" s="0"/>
+      <c r="K63" s="0"/>
+      <c r="L63" s="0"/>
     </row>
     <row r="64">
       <c r="A64" s="0" t="s">
@@ -1384,6 +1512,8 @@
       <c r="H64" s="0"/>
       <c r="I64" s="0"/>
       <c r="J64" s="0"/>
+      <c r="K64" s="0"/>
+      <c r="L64" s="0"/>
     </row>
     <row r="65">
       <c r="A65" s="0" t="s">
@@ -1398,6 +1528,8 @@
       <c r="H65" s="0"/>
       <c r="I65" s="0"/>
       <c r="J65" s="0"/>
+      <c r="K65" s="0"/>
+      <c r="L65" s="0"/>
     </row>
     <row r="66">
       <c r="A66" s="0"/>
@@ -1410,6 +1542,8 @@
       <c r="H66" s="0"/>
       <c r="I66" s="0"/>
       <c r="J66" s="0"/>
+      <c r="K66" s="0"/>
+      <c r="L66" s="0"/>
     </row>
     <row r="67">
       <c r="A67" s="0" t="s">
@@ -1426,6 +1560,8 @@
       <c r="H67" s="0"/>
       <c r="I67" s="0"/>
       <c r="J67" s="0"/>
+      <c r="K67" s="0"/>
+      <c r="L67" s="0"/>
     </row>
     <row r="68">
       <c r="A68" s="0" t="s">
@@ -1442,6 +1578,8 @@
       <c r="H68" s="0"/>
       <c r="I68" s="0"/>
       <c r="J68" s="0"/>
+      <c r="K68" s="0"/>
+      <c r="L68" s="0"/>
     </row>
     <row r="69">
       <c r="A69" s="0" t="s">
@@ -1458,6 +1596,8 @@
       <c r="H69" s="0"/>
       <c r="I69" s="0"/>
       <c r="J69" s="0"/>
+      <c r="K69" s="0"/>
+      <c r="L69" s="0"/>
     </row>
     <row r="70">
       <c r="A70" s="0" t="s">
@@ -1472,6 +1612,8 @@
       <c r="H70" s="0"/>
       <c r="I70" s="0"/>
       <c r="J70" s="0"/>
+      <c r="K70" s="0"/>
+      <c r="L70" s="0"/>
     </row>
     <row r="71">
       <c r="A71" s="0"/>
@@ -1484,6 +1626,8 @@
       <c r="H71" s="0"/>
       <c r="I71" s="0"/>
       <c r="J71" s="0"/>
+      <c r="K71" s="0"/>
+      <c r="L71" s="0"/>
     </row>
     <row r="72">
       <c r="A72" s="0"/>
@@ -1496,6 +1640,8 @@
       <c r="H72" s="0"/>
       <c r="I72" s="0"/>
       <c r="J72" s="0"/>
+      <c r="K72" s="0"/>
+      <c r="L72" s="0"/>
     </row>
     <row r="73">
       <c r="A73" s="0" t="s">
@@ -1510,6 +1656,8 @@
       <c r="H73" s="0"/>
       <c r="I73" s="0"/>
       <c r="J73" s="0"/>
+      <c r="K73" s="0"/>
+      <c r="L73" s="0"/>
     </row>
     <row r="74">
       <c r="A74" s="0" t="s">
@@ -1526,6 +1674,8 @@
       <c r="H74" s="0"/>
       <c r="I74" s="0"/>
       <c r="J74" s="0"/>
+      <c r="K74" s="0"/>
+      <c r="L74" s="0"/>
     </row>
     <row r="75">
       <c r="A75" s="0" t="s">
@@ -1542,6 +1692,8 @@
       <c r="H75" s="0"/>
       <c r="I75" s="0"/>
       <c r="J75" s="0"/>
+      <c r="K75" s="0"/>
+      <c r="L75" s="0"/>
     </row>
     <row r="76">
       <c r="A76" s="0"/>
@@ -1556,6 +1708,8 @@
       <c r="H76" s="0"/>
       <c r="I76" s="0"/>
       <c r="J76" s="0"/>
+      <c r="K76" s="0"/>
+      <c r="L76" s="0"/>
     </row>
     <row r="77">
       <c r="A77" s="0" t="s">
@@ -1576,6 +1730,8 @@
       <c r="H77" s="0"/>
       <c r="I77" s="0"/>
       <c r="J77" s="0"/>
+      <c r="K77" s="0"/>
+      <c r="L77" s="0"/>
     </row>
     <row r="78">
       <c r="A78" s="0" t="s">
@@ -1590,6 +1746,8 @@
       <c r="H78" s="0"/>
       <c r="I78" s="0"/>
       <c r="J78" s="0"/>
+      <c r="K78" s="0"/>
+      <c r="L78" s="0"/>
     </row>
     <row r="79">
       <c r="A79" s="0"/>
@@ -1602,6 +1760,8 @@
       <c r="H79" s="0"/>
       <c r="I79" s="0"/>
       <c r="J79" s="0"/>
+      <c r="K79" s="0"/>
+      <c r="L79" s="0"/>
     </row>
     <row r="80">
       <c r="A80" s="0"/>
@@ -1614,6 +1774,8 @@
       <c r="H80" s="0"/>
       <c r="I80" s="0"/>
       <c r="J80" s="0"/>
+      <c r="K80" s="0"/>
+      <c r="L80" s="0"/>
     </row>
     <row r="81">
       <c r="A81" s="0" t="s">
@@ -1628,6 +1790,8 @@
       <c r="H81" s="0"/>
       <c r="I81" s="0"/>
       <c r="J81" s="0"/>
+      <c r="K81" s="0"/>
+      <c r="L81" s="0"/>
     </row>
     <row r="82">
       <c r="A82" s="0" t="s">
@@ -1644,6 +1808,8 @@
       <c r="H82" s="0"/>
       <c r="I82" s="0"/>
       <c r="J82" s="0"/>
+      <c r="K82" s="0"/>
+      <c r="L82" s="0"/>
     </row>
     <row r="83">
       <c r="A83" s="0" t="s">
@@ -1660,6 +1826,8 @@
       <c r="H83" s="0"/>
       <c r="I83" s="0"/>
       <c r="J83" s="0"/>
+      <c r="K83" s="0"/>
+      <c r="L83" s="0"/>
     </row>
     <row r="84">
       <c r="A84" s="0"/>
@@ -1674,6 +1842,8 @@
       <c r="H84" s="0"/>
       <c r="I84" s="0"/>
       <c r="J84" s="0"/>
+      <c r="K84" s="0"/>
+      <c r="L84" s="0"/>
     </row>
     <row r="85">
       <c r="A85" s="0" t="s">
@@ -1702,6 +1872,8 @@
       </c>
       <c r="I85" s="0"/>
       <c r="J85" s="0"/>
+      <c r="K85" s="0"/>
+      <c r="L85" s="0"/>
     </row>
     <row r="86">
       <c r="A86" s="0" t="s">
@@ -1720,6 +1892,8 @@
       <c r="H86" s="0"/>
       <c r="I86" s="0"/>
       <c r="J86" s="0"/>
+      <c r="K86" s="0"/>
+      <c r="L86" s="0"/>
     </row>
     <row r="87">
       <c r="A87" s="0" t="s">
@@ -1738,6 +1912,8 @@
       <c r="H87" s="0"/>
       <c r="I87" s="0"/>
       <c r="J87" s="0"/>
+      <c r="K87" s="0"/>
+      <c r="L87" s="0"/>
     </row>
     <row r="88">
       <c r="A88" s="0" t="s">
@@ -1756,6 +1932,8 @@
       <c r="H88" s="0"/>
       <c r="I88" s="0"/>
       <c r="J88" s="0"/>
+      <c r="K88" s="0"/>
+      <c r="L88" s="0"/>
     </row>
     <row r="89">
       <c r="A89" s="0" t="s">
@@ -1774,6 +1952,8 @@
       <c r="H89" s="0"/>
       <c r="I89" s="0"/>
       <c r="J89" s="0"/>
+      <c r="K89" s="0"/>
+      <c r="L89" s="0"/>
     </row>
     <row r="90">
       <c r="A90" s="0" t="s">
@@ -1792,6 +1972,8 @@
       <c r="H90" s="0"/>
       <c r="I90" s="0"/>
       <c r="J90" s="0"/>
+      <c r="K90" s="0"/>
+      <c r="L90" s="0"/>
     </row>
     <row r="91">
       <c r="A91" s="0" t="s">
@@ -1810,6 +1992,8 @@
       <c r="H91" s="0"/>
       <c r="I91" s="0"/>
       <c r="J91" s="0"/>
+      <c r="K91" s="0"/>
+      <c r="L91" s="0"/>
     </row>
     <row r="92">
       <c r="A92" s="0" t="s">
@@ -1828,6 +2012,8 @@
       <c r="H92" s="0"/>
       <c r="I92" s="0"/>
       <c r="J92" s="0"/>
+      <c r="K92" s="0"/>
+      <c r="L92" s="0"/>
     </row>
     <row r="93">
       <c r="A93" s="0" t="s">
@@ -1846,6 +2032,8 @@
       <c r="H93" s="0"/>
       <c r="I93" s="0"/>
       <c r="J93" s="0"/>
+      <c r="K93" s="0"/>
+      <c r="L93" s="0"/>
     </row>
     <row r="94">
       <c r="A94" s="0" t="s">
@@ -1860,6 +2048,8 @@
       <c r="H94" s="0"/>
       <c r="I94" s="0"/>
       <c r="J94" s="0"/>
+      <c r="K94" s="0"/>
+      <c r="L94" s="0"/>
     </row>
     <row r="95">
       <c r="A95" s="0"/>
@@ -1872,6 +2062,8 @@
       <c r="H95" s="0"/>
       <c r="I95" s="0"/>
       <c r="J95" s="0"/>
+      <c r="K95" s="0"/>
+      <c r="L95" s="0"/>
     </row>
     <row r="96">
       <c r="A96" s="0"/>
@@ -1884,6 +2076,8 @@
       <c r="H96" s="0"/>
       <c r="I96" s="0"/>
       <c r="J96" s="0"/>
+      <c r="K96" s="0"/>
+      <c r="L96" s="0"/>
     </row>
     <row r="97">
       <c r="A97" s="0" t="s">
@@ -1898,6 +2092,8 @@
       <c r="H97" s="0"/>
       <c r="I97" s="0"/>
       <c r="J97" s="0"/>
+      <c r="K97" s="0"/>
+      <c r="L97" s="0"/>
     </row>
     <row r="98">
       <c r="A98" s="0" t="s">
@@ -1914,6 +2110,8 @@
       <c r="H98" s="0"/>
       <c r="I98" s="0"/>
       <c r="J98" s="0"/>
+      <c r="K98" s="0"/>
+      <c r="L98" s="0"/>
     </row>
     <row r="99">
       <c r="A99" s="0" t="s">
@@ -1930,6 +2128,8 @@
       <c r="H99" s="0"/>
       <c r="I99" s="0"/>
       <c r="J99" s="0"/>
+      <c r="K99" s="0"/>
+      <c r="L99" s="0"/>
     </row>
     <row r="100">
       <c r="A100" s="0"/>
@@ -1944,6 +2144,8 @@
       <c r="H100" s="0"/>
       <c r="I100" s="0"/>
       <c r="J100" s="0"/>
+      <c r="K100" s="0"/>
+      <c r="L100" s="0"/>
     </row>
     <row r="101">
       <c r="A101" s="0" t="s">
@@ -1964,6 +2166,8 @@
       <c r="H101" s="0"/>
       <c r="I101" s="0"/>
       <c r="J101" s="0"/>
+      <c r="K101" s="0"/>
+      <c r="L101" s="0"/>
     </row>
     <row r="102">
       <c r="A102" s="0" t="s">
@@ -1984,6 +2188,8 @@
       <c r="H102" s="0"/>
       <c r="I102" s="0"/>
       <c r="J102" s="0"/>
+      <c r="K102" s="0"/>
+      <c r="L102" s="0"/>
     </row>
     <row r="103">
       <c r="A103" s="0" t="s">
@@ -2004,6 +2210,8 @@
       <c r="H103" s="0"/>
       <c r="I103" s="0"/>
       <c r="J103" s="0"/>
+      <c r="K103" s="0"/>
+      <c r="L103" s="0"/>
     </row>
     <row r="104">
       <c r="A104" s="0" t="s">
@@ -2022,6 +2230,8 @@
       <c r="H104" s="0"/>
       <c r="I104" s="0"/>
       <c r="J104" s="0"/>
+      <c r="K104" s="0"/>
+      <c r="L104" s="0"/>
     </row>
     <row r="105">
       <c r="A105" s="0" t="s">
@@ -2036,6 +2246,8 @@
       <c r="H105" s="0"/>
       <c r="I105" s="0"/>
       <c r="J105" s="0"/>
+      <c r="K105" s="0"/>
+      <c r="L105" s="0"/>
     </row>
     <row r="106">
       <c r="A106" s="0"/>
@@ -2048,6 +2260,8 @@
       <c r="H106" s="0"/>
       <c r="I106" s="0"/>
       <c r="J106" s="0"/>
+      <c r="K106" s="0"/>
+      <c r="L106" s="0"/>
     </row>
     <row r="107">
       <c r="A107" s="0"/>
@@ -2060,6 +2274,8 @@
       <c r="H107" s="0"/>
       <c r="I107" s="0"/>
       <c r="J107" s="0"/>
+      <c r="K107" s="0"/>
+      <c r="L107" s="0"/>
     </row>
     <row r="108">
       <c r="A108" s="0" t="s">
@@ -2074,6 +2290,8 @@
       <c r="H108" s="0"/>
       <c r="I108" s="0"/>
       <c r="J108" s="0"/>
+      <c r="K108" s="0"/>
+      <c r="L108" s="0"/>
     </row>
     <row r="109">
       <c r="A109" s="0" t="s">
@@ -2090,6 +2308,8 @@
       <c r="H109" s="0"/>
       <c r="I109" s="0"/>
       <c r="J109" s="0"/>
+      <c r="K109" s="0"/>
+      <c r="L109" s="0"/>
     </row>
     <row r="110">
       <c r="A110" s="0" t="s">
@@ -2106,6 +2326,8 @@
       <c r="H110" s="0"/>
       <c r="I110" s="0"/>
       <c r="J110" s="0"/>
+      <c r="K110" s="0"/>
+      <c r="L110" s="0"/>
     </row>
     <row r="111">
       <c r="A111" s="0" t="s">
@@ -2134,6 +2356,8 @@
       </c>
       <c r="I111" s="0"/>
       <c r="J111" s="0"/>
+      <c r="K111" s="0"/>
+      <c r="L111" s="0"/>
     </row>
     <row r="112">
       <c r="A112" s="0" t="s">
@@ -2150,6 +2374,8 @@
       <c r="H112" s="0"/>
       <c r="I112" s="0"/>
       <c r="J112" s="0"/>
+      <c r="K112" s="0"/>
+      <c r="L112" s="0"/>
     </row>
     <row r="113">
       <c r="A113" s="0" t="s">
@@ -2166,6 +2392,8 @@
       <c r="H113" s="0"/>
       <c r="I113" s="0"/>
       <c r="J113" s="0"/>
+      <c r="K113" s="0"/>
+      <c r="L113" s="0"/>
     </row>
     <row r="114">
       <c r="A114" s="0" t="s">
@@ -2182,6 +2410,8 @@
       <c r="H114" s="0"/>
       <c r="I114" s="0"/>
       <c r="J114" s="0"/>
+      <c r="K114" s="0"/>
+      <c r="L114" s="0"/>
     </row>
     <row r="115">
       <c r="A115" s="0" t="s">
@@ -2198,6 +2428,8 @@
       <c r="H115" s="0"/>
       <c r="I115" s="0"/>
       <c r="J115" s="0"/>
+      <c r="K115" s="0"/>
+      <c r="L115" s="0"/>
     </row>
     <row r="116">
       <c r="A116" s="0" t="s">
@@ -2214,6 +2446,8 @@
       <c r="H116" s="0"/>
       <c r="I116" s="0"/>
       <c r="J116" s="0"/>
+      <c r="K116" s="0"/>
+      <c r="L116" s="0"/>
     </row>
     <row r="117">
       <c r="A117" s="0" t="s">
@@ -2230,6 +2464,8 @@
       <c r="H117" s="0"/>
       <c r="I117" s="0"/>
       <c r="J117" s="0"/>
+      <c r="K117" s="0"/>
+      <c r="L117" s="0"/>
     </row>
     <row r="118">
       <c r="A118" s="0" t="s">
@@ -2246,6 +2482,8 @@
       <c r="H118" s="0"/>
       <c r="I118" s="0"/>
       <c r="J118" s="0"/>
+      <c r="K118" s="0"/>
+      <c r="L118" s="0"/>
     </row>
     <row r="119">
       <c r="A119" s="0" t="s">
@@ -2260,6 +2498,8 @@
       <c r="H119" s="0"/>
       <c r="I119" s="0"/>
       <c r="J119" s="0"/>
+      <c r="K119" s="0"/>
+      <c r="L119" s="0"/>
     </row>
     <row r="120">
       <c r="A120" s="0"/>
@@ -2272,6 +2512,8 @@
       <c r="H120" s="0"/>
       <c r="I120" s="0"/>
       <c r="J120" s="0"/>
+      <c r="K120" s="0"/>
+      <c r="L120" s="0"/>
     </row>
     <row r="121">
       <c r="A121" s="0"/>
@@ -2284,6 +2526,8 @@
       <c r="H121" s="0"/>
       <c r="I121" s="0"/>
       <c r="J121" s="0"/>
+      <c r="K121" s="0"/>
+      <c r="L121" s="0"/>
     </row>
   </sheetData>
 </worksheet>
